--- a/data/leagues/Operators Football League 2026.xlsx
+++ b/data/leagues/Operators Football League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="95">
   <si>
     <t>Junya Ettlinger's First Team</t>
   </si>
@@ -55,10 +55,13 @@
     <t>Hall Pass</t>
   </si>
   <si>
-    <t>0-1-0</t>
-  </si>
-  <si>
-    <t>1-0-0</t>
+    <t>1-1-0</t>
+  </si>
+  <si>
+    <t>2-0-0</t>
+  </si>
+  <si>
+    <t>0-2-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -118,6 +121,9 @@
     <t>Week_2</t>
   </si>
   <si>
+    <t>Week_3</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -139,24 +145,24 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Rachel Hall</t>
+  </si>
+  <si>
     <t>Julie Williston</t>
   </si>
   <si>
+    <t>Haley Toadvine</t>
+  </si>
+  <si>
     <t>Casey Reid</t>
   </si>
   <si>
-    <t>Rachel Hall</t>
-  </si>
-  <si>
     <t>Carly Foster</t>
   </si>
   <si>
     <t>Jessica McNally</t>
   </si>
   <si>
-    <t>Haley Toadvine</t>
-  </si>
-  <si>
     <t>Morgan Herber</t>
   </si>
   <si>
@@ -193,58 +199,58 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>0-1</t>
-  </si>
-  <si>
-    <t>9.7-4.2-0.1</t>
-  </si>
-  <si>
-    <t>9.8-4.1-0.1</t>
-  </si>
-  <si>
-    <t>9.6-4.3-0.1</t>
-  </si>
-  <si>
-    <t>9.5-4.4-0.1</t>
-  </si>
-  <si>
-    <t>8.2-5.7-0.1</t>
-  </si>
-  <si>
-    <t>7.5-6.3-0.1</t>
-  </si>
-  <si>
-    <t>6.6-7.3-0.1</t>
-  </si>
-  <si>
-    <t>3.9-10.0-0.1</t>
-  </si>
-  <si>
-    <t>2.6-11.3-0.1</t>
-  </si>
-  <si>
-    <t>2.0-11.9-0.1</t>
-  </si>
-  <si>
-    <t>10-4</t>
+    <t>2-0</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>0-2</t>
+  </si>
+  <si>
+    <t>10.8-3.0-0.2</t>
+  </si>
+  <si>
+    <t>11.8-2.1-0.1</t>
+  </si>
+  <si>
+    <t>8.5-5.4-0.1</t>
+  </si>
+  <si>
+    <t>7.5-6.4-0.1</t>
+  </si>
+  <si>
+    <t>6.8-7.1-0.1</t>
+  </si>
+  <si>
+    <t>6.0-7.9-0.1</t>
+  </si>
+  <si>
+    <t>5.7-8.2-0.1</t>
+  </si>
+  <si>
+    <t>5.5-8.4-0.1</t>
+  </si>
+  <si>
+    <t>1.3-12.6-0.1</t>
+  </si>
+  <si>
+    <t>11-3</t>
+  </si>
+  <si>
+    <t>12-2</t>
   </si>
   <si>
     <t>9-5</t>
   </si>
   <si>
-    <t>8-6</t>
+    <t>7-7</t>
   </si>
   <si>
     <t>6-8</t>
   </si>
   <si>
-    <t>4-10</t>
-  </si>
-  <si>
-    <t>2-12</t>
+    <t>1-13</t>
   </si>
   <si>
     <t>Owners</t>
@@ -256,7 +262,31 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
     <t>Week 1</t>
+  </si>
+  <si>
+    <t>Week 2</t>
   </si>
   <si>
     <t>Week</t>
@@ -678,16 +708,16 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
@@ -696,7 +726,7 @@
         <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
         <v>11</v>
@@ -710,34 +740,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J3" t="s">
         <v>11</v>
       </c>
       <c r="K3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -748,16 +778,16 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -766,13 +796,13 @@
         <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J4" t="s">
         <v>11</v>
       </c>
       <c r="K4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -780,34 +810,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J5" t="s">
         <v>10</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -818,31 +848,31 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J6" t="s">
         <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -862,7 +892,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>10</v>
@@ -871,7 +901,7 @@
         <v>11</v>
       </c>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J7" t="s">
         <v>10</v>
@@ -906,7 +936,7 @@
         <v>11</v>
       </c>
       <c r="I8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J8" t="s">
         <v>11</v>
@@ -920,34 +950,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -993,7 +1023,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1002,7 +1032,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
@@ -1011,7 +1041,7 @@
         <v>11</v>
       </c>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J11" t="s">
         <v>10</v>
@@ -1027,30 +1057,82 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:8">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>-4</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1065,13 +1147,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1079,13 +1161,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1093,10 +1175,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1110,10 +1192,10 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1121,10 +1203,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1135,13 +1217,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1149,13 +1231,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1163,13 +1245,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1180,7 +1262,7 @@
         <v>9</v>
       </c>
       <c r="C9">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1191,10 +1273,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -1208,7 +1290,7 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -1226,16 +1308,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1243,13 +1325,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -1260,13 +1342,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="D3">
-        <v>-0.09999999999999998</v>
+        <v>-0.2</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -1277,16 +1359,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="D4">
-        <v>-0.2</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1294,16 +1376,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="D5">
-        <v>-0.3</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1311,13 +1393,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1328,16 +1410,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="D7">
-        <v>-0.6</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1345,13 +1427,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="D8">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1362,13 +1444,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="D9">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -1379,16 +1461,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="D10">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1405,7 +1487,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1420,40 +1502,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1461,66 +1543,66 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>21.2</v>
+        <v>23.3</v>
       </c>
       <c r="C2">
-        <v>22.8</v>
+        <v>59.6</v>
       </c>
       <c r="D2">
-        <v>20.1</v>
+        <v>12.9</v>
       </c>
       <c r="E2">
-        <v>14.6</v>
+        <v>3.1</v>
       </c>
       <c r="F2">
-        <v>13.3</v>
+        <v>0.9</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>0.2</v>
       </c>
       <c r="H2">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>32.2</v>
+        <v>73.7</v>
       </c>
       <c r="C3">
-        <v>20.2</v>
+        <v>21.7</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>4.1</v>
       </c>
       <c r="E3">
-        <v>15.8</v>
+        <v>0.4</v>
       </c>
       <c r="F3">
-        <v>8.699999999999999</v>
+        <v>0.1</v>
       </c>
       <c r="G3">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1529,197 +1611,197 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>97.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4">
-        <v>20</v>
+        <v>1.4</v>
       </c>
       <c r="C4">
-        <v>19.2</v>
+        <v>9.5</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>41.6</v>
       </c>
       <c r="E4">
-        <v>17.5</v>
+        <v>24.6</v>
       </c>
       <c r="F4">
-        <v>12.4</v>
+        <v>13.2</v>
       </c>
       <c r="G4">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="I4">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>96.8</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B5">
-        <v>18.9</v>
+        <v>1.1</v>
       </c>
       <c r="C5">
-        <v>21.9</v>
+        <v>5.7</v>
       </c>
       <c r="D5">
-        <v>19.3</v>
+        <v>21.5</v>
       </c>
       <c r="E5">
-        <v>15.7</v>
+        <v>24.8</v>
       </c>
       <c r="F5">
-        <v>12.5</v>
+        <v>18.2</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>12.3</v>
       </c>
       <c r="H5">
-        <v>3.1</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L5">
-        <v>96.3</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>14.3</v>
+        <v>10.3</v>
       </c>
       <c r="E6">
-        <v>18.1</v>
+        <v>16.4</v>
       </c>
       <c r="F6">
-        <v>21.2</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>18</v>
+        <v>15.4</v>
       </c>
       <c r="H6">
-        <v>11.4</v>
+        <v>13.2</v>
       </c>
       <c r="I6">
-        <v>1.7</v>
+        <v>12.3</v>
       </c>
       <c r="J6">
-        <v>0.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L6">
-        <v>86.8</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="D7">
-        <v>7.1</v>
+        <v>4.6</v>
       </c>
       <c r="E7">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>21.6</v>
+        <v>12.4</v>
       </c>
       <c r="G7">
-        <v>30.4</v>
+        <v>14.2</v>
       </c>
       <c r="H7">
-        <v>20.2</v>
+        <v>17.9</v>
       </c>
       <c r="I7">
-        <v>2.7</v>
+        <v>18.5</v>
       </c>
       <c r="J7">
-        <v>0.1</v>
+        <v>20</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L7">
-        <v>77</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="D8">
         <v>3.2</v>
       </c>
       <c r="E8">
-        <v>6.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F8">
-        <v>9.800000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="G8">
-        <v>22.2</v>
+        <v>16.9</v>
       </c>
       <c r="H8">
-        <v>43.1</v>
+        <v>16.3</v>
       </c>
       <c r="I8">
-        <v>11.9</v>
+        <v>19.1</v>
       </c>
       <c r="J8">
-        <v>1.2</v>
+        <v>21.6</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L8">
-        <v>43.8</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1730,39 +1812,39 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E9">
-        <v>0.2</v>
+        <v>6.1</v>
       </c>
       <c r="F9">
-        <v>0.4</v>
+        <v>10.8</v>
       </c>
       <c r="G9">
-        <v>2.4</v>
+        <v>17.3</v>
       </c>
       <c r="H9">
-        <v>11.9</v>
+        <v>19.5</v>
       </c>
       <c r="I9">
-        <v>53.7</v>
+        <v>20.9</v>
       </c>
       <c r="J9">
-        <v>22</v>
+        <v>23.4</v>
       </c>
       <c r="K9">
-        <v>9.4</v>
+        <v>0.9</v>
       </c>
       <c r="L9">
-        <v>3</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1771,31 +1853,31 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="F10">
+        <v>11.5</v>
+      </c>
+      <c r="G10">
+        <v>17.8</v>
+      </c>
+      <c r="H10">
+        <v>22.4</v>
+      </c>
+      <c r="I10">
+        <v>22.7</v>
+      </c>
+      <c r="J10">
+        <v>19.7</v>
+      </c>
+      <c r="K10">
         <v>0.1</v>
       </c>
-      <c r="G10">
-        <v>0.4</v>
-      </c>
-      <c r="H10">
-        <v>2.6</v>
-      </c>
-      <c r="I10">
-        <v>19.3</v>
-      </c>
-      <c r="J10">
-        <v>45.7</v>
-      </c>
-      <c r="K10">
-        <v>31.9</v>
-      </c>
       <c r="L10">
-        <v>0.5</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1818,22 +1900,22 @@
         <v>0</v>
       </c>
       <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0.2</v>
+      </c>
+      <c r="I11">
         <v>0.1</v>
       </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>9.4</v>
-      </c>
       <c r="J11">
-        <v>30.8</v>
+        <v>2.4</v>
       </c>
       <c r="K11">
-        <v>58.7</v>
+        <v>97.3</v>
       </c>
       <c r="L11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1843,117 +1925,147 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>95.7</v>
+      </c>
+      <c r="C3">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="C4">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="D4">
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>98.7</v>
-      </c>
-      <c r="C2">
-        <v>97.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
+      <c r="B5">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="C5">
+        <v>86.8</v>
+      </c>
+      <c r="D5">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>98</v>
-      </c>
-      <c r="C3">
-        <v>97.39999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="C4">
-        <v>97.09999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>95.5</v>
-      </c>
-      <c r="C5">
-        <v>95.8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="B6">
-        <v>86.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="C6">
-        <v>87.40000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>69.8</v>
+      </c>
+      <c r="D6">
+        <v>65.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.5</v>
+      </c>
+      <c r="C7">
+        <v>48.5</v>
+      </c>
+      <c r="D7">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B7">
-        <v>73.3</v>
-      </c>
-      <c r="C7">
-        <v>79.40000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
+      <c r="B8">
+        <v>72.3</v>
+      </c>
+      <c r="C8">
+        <v>40.6</v>
+      </c>
+      <c r="D8">
+        <v>40.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B8">
-        <v>46.9</v>
-      </c>
-      <c r="C8">
-        <v>40.40000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
+      <c r="B9">
+        <v>47.3</v>
+      </c>
+      <c r="C9">
+        <v>24.5</v>
+      </c>
+      <c r="D9">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9">
-        <v>2.8</v>
-      </c>
-      <c r="C9">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B10">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>0.7000000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>33.90000000000001</v>
+      </c>
+      <c r="D10">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1961,7 +2073,10 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1976,28 +2091,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2005,28 +2120,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2">
-        <v>110.4</v>
+        <v>103.55</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>118.17</v>
+        <v>112.78</v>
       </c>
       <c r="G2">
-        <v>0.538</v>
+        <v>0.583</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2034,28 +2149,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>74.7</v>
+        <v>104.6</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3">
-        <v>120.1</v>
+        <v>112.11</v>
       </c>
       <c r="G3">
-        <v>0.538</v>
+        <v>0.542</v>
       </c>
       <c r="H3">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2063,28 +2178,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4">
-        <v>92.62</v>
+        <v>119.52</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>116.4</v>
+        <v>112.86</v>
       </c>
       <c r="G4">
-        <v>0.615</v>
+        <v>0.583</v>
       </c>
       <c r="H4">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2092,28 +2207,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5">
-        <v>120.06</v>
+        <v>75.63</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>109.35</v>
+        <v>112.09</v>
       </c>
       <c r="G5">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H5">
         <v>0.2</v>
       </c>
       <c r="I5">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2121,28 +2236,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>79.95999999999999</v>
+        <v>103.72</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>117.08</v>
+        <v>105.99</v>
       </c>
       <c r="G6">
-        <v>0.538</v>
+        <v>0.5</v>
       </c>
       <c r="H6">
         <v>-0.1</v>
       </c>
       <c r="I6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2150,28 +2265,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D7">
-        <v>136.06</v>
+        <v>101.3</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>113.44</v>
+        <v>110.72</v>
       </c>
       <c r="G7">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H7">
         <v>-0.2</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2182,25 +2297,25 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8">
-        <v>128.32</v>
+        <v>118.29</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8">
-        <v>111.01</v>
+        <v>106.26</v>
       </c>
       <c r="G8">
-        <v>0.538</v>
+        <v>0.458</v>
       </c>
       <c r="H8">
         <v>-0.3</v>
       </c>
       <c r="I8">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2211,25 +2326,25 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D9">
-        <v>130.66</v>
+        <v>129.03</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9">
-        <v>109.12</v>
+        <v>107.41</v>
       </c>
       <c r="G9">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="H9">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="I9">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2240,25 +2355,25 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10">
-        <v>128.46</v>
+        <v>105.04</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>106.68</v>
+        <v>106.04</v>
       </c>
       <c r="G10">
-        <v>0.385</v>
+        <v>0.417</v>
       </c>
       <c r="H10">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2269,25 +2384,25 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>128.96</v>
+        <v>132.94</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11">
-        <v>108.85</v>
+        <v>107.36</v>
       </c>
       <c r="G11">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="H11">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2302,31 +2417,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2334,202 +2449,202 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>130.66</v>
+        <v>129.03</v>
       </c>
       <c r="E2">
-        <v>130.66</v>
+        <v>258.06</v>
       </c>
       <c r="F2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>136.06</v>
+        <v>132.94</v>
       </c>
       <c r="E3">
-        <v>136.06</v>
+        <v>265.88</v>
       </c>
       <c r="F3">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D4">
-        <v>128.46</v>
+        <v>118.29</v>
       </c>
       <c r="E4">
-        <v>128.46</v>
+        <v>236.58</v>
       </c>
       <c r="F4">
-        <v>96.8</v>
+        <v>96.2</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>128.96</v>
+        <v>119.52</v>
       </c>
       <c r="E5">
-        <v>128.96</v>
+        <v>239.04</v>
       </c>
       <c r="F5">
-        <v>96.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>128.32</v>
+        <v>105.04</v>
       </c>
       <c r="E6">
-        <v>128.32</v>
+        <v>210.08</v>
       </c>
       <c r="F6">
-        <v>86.8</v>
+        <v>64.60000000000001</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>120.06</v>
+        <v>101.3</v>
       </c>
       <c r="E7">
-        <v>120.06</v>
+        <v>202.6</v>
       </c>
       <c r="F7">
-        <v>77</v>
+        <v>42.8</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>110.4</v>
+        <v>103.72</v>
       </c>
       <c r="E8">
-        <v>110.4</v>
+        <v>207.44</v>
       </c>
       <c r="F8">
-        <v>43.8</v>
+        <v>42.4</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2537,57 +2652,57 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>92.62</v>
+        <v>103.55</v>
       </c>
       <c r="E9">
-        <v>92.62</v>
+        <v>207.1</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>35.3</v>
       </c>
       <c r="G9">
-        <v>9.4</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="H9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>79.95999999999999</v>
+        <v>104.6</v>
       </c>
       <c r="E10">
-        <v>79.95999999999999</v>
+        <v>209.2</v>
       </c>
       <c r="F10">
-        <v>0.5</v>
+        <v>35.09999999999999</v>
       </c>
       <c r="G10">
-        <v>31.9</v>
+        <v>0.1</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2595,28 +2710,28 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>74.7</v>
+        <v>75.63</v>
       </c>
       <c r="E11">
-        <v>74.7</v>
+        <v>151.26</v>
       </c>
       <c r="F11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>58.7</v>
+        <v>97.3</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2631,19 +2746,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2651,19 +2766,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2">
-        <v>0</v>
+      <c r="F2" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2671,7 +2786,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>47</v>
@@ -2682,8 +2797,8 @@
       <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="F3">
-        <v>0</v>
+      <c r="F3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2694,16 +2809,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2711,10 +2826,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2722,8 +2837,8 @@
       <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="F5">
-        <v>0</v>
+      <c r="F5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2731,19 +2846,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="F6">
-        <v>0</v>
+      <c r="F6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2754,7 +2869,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -2762,8 +2877,8 @@
       <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F7">
-        <v>0</v>
+      <c r="F7" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2771,19 +2886,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2791,10 +2906,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9">
         <v>-2</v>
@@ -2802,8 +2917,8 @@
       <c r="E9" t="s">
         <v>10</v>
       </c>
-      <c r="F9">
-        <v>0</v>
+      <c r="F9" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2811,19 +2926,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D10">
         <v>-4</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2837,13 +2952,13 @@
         <v>40</v>
       </c>
       <c r="D11">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
-      <c r="F11">
-        <v>0</v>
+      <c r="F11" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2853,40 +2968,49 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>87</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>4</v>
       </c>
       <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2894,23 +3018,29 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -2918,8 +3048,11 @@
       <c r="C6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -2929,41 +3062,53 @@
       <c r="C7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>-2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>-4</v>
+      </c>
+      <c r="C9">
+        <v>-2</v>
+      </c>
+      <c r="D9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>-2</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10">
+      <c r="C10">
         <v>-4</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -2971,7 +3116,10 @@
         <v>-6</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Operators Football League 2026.xlsx
+++ b/data/leagues/Operators Football League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="96">
   <si>
     <t>Junya Ettlinger's First Team</t>
   </si>
@@ -208,10 +208,10 @@
     <t>0-2</t>
   </si>
   <si>
-    <t>10.8-3.0-0.2</t>
-  </si>
-  <si>
-    <t>11.8-2.1-0.1</t>
+    <t>10.9-3.0-0.1</t>
+  </si>
+  <si>
+    <t>11.7-2.2-0.1</t>
   </si>
   <si>
     <t>8.5-5.4-0.1</t>
@@ -220,13 +220,16 @@
     <t>7.5-6.4-0.1</t>
   </si>
   <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>6.0-7.9-0.1</t>
-  </si>
-  <si>
-    <t>5.7-8.2-0.1</t>
+    <t>6.9-7.0-0.1</t>
+  </si>
+  <si>
+    <t>6.1-7.8-0.1</t>
+  </si>
+  <si>
+    <t>5.6-8.3-0.1</t>
+  </si>
+  <si>
+    <t>5.4-8.4-0.1</t>
   </si>
   <si>
     <t>5.5-8.4-0.1</t>
@@ -1062,25 +1065,25 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1543,22 +1546,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>23.3</v>
+        <v>23.9</v>
       </c>
       <c r="C2">
-        <v>59.6</v>
+        <v>58.8</v>
       </c>
       <c r="D2">
-        <v>12.9</v>
+        <v>14.1</v>
       </c>
       <c r="E2">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="F2">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1581,22 +1584,22 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>73.7</v>
+        <v>71.3</v>
       </c>
       <c r="C3">
-        <v>21.7</v>
+        <v>24.3</v>
       </c>
       <c r="D3">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="E3">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>0.1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1619,37 +1622,37 @@
         <v>0</v>
       </c>
       <c r="B4">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="C4">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="D4">
-        <v>41.6</v>
+        <v>38.9</v>
       </c>
       <c r="E4">
-        <v>24.6</v>
+        <v>27.2</v>
       </c>
       <c r="F4">
         <v>13.2</v>
       </c>
       <c r="G4">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="H4">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="I4">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J4">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>96.2</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1657,37 +1660,37 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="C5">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="D5">
-        <v>21.5</v>
+        <v>19.8</v>
       </c>
       <c r="E5">
-        <v>24.8</v>
+        <v>26.8</v>
       </c>
       <c r="F5">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>12.3</v>
+        <v>13.5</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="J5">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="K5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>83.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1698,34 +1701,34 @@
         <v>0.5</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="D6">
-        <v>10.3</v>
+        <v>12.8</v>
       </c>
       <c r="E6">
-        <v>16.4</v>
+        <v>14.9</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="G6">
-        <v>15.4</v>
+        <v>14.6</v>
       </c>
       <c r="H6">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
       <c r="I6">
-        <v>12.3</v>
+        <v>11.2</v>
       </c>
       <c r="J6">
-        <v>9.699999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="K6">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L6">
-        <v>64.59999999999999</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1736,34 +1739,34 @@
         <v>0</v>
       </c>
       <c r="C7">
+        <v>0.8</v>
+      </c>
+      <c r="D7">
+        <v>5.8</v>
+      </c>
+      <c r="E7">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F7">
+        <v>12.9</v>
+      </c>
+      <c r="G7">
+        <v>17.8</v>
+      </c>
+      <c r="H7">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <v>16.5</v>
+      </c>
+      <c r="J7">
+        <v>17.9</v>
+      </c>
+      <c r="K7">
         <v>0.6</v>
       </c>
-      <c r="D7">
-        <v>4.6</v>
-      </c>
-      <c r="E7">
-        <v>11</v>
-      </c>
-      <c r="F7">
-        <v>12.4</v>
-      </c>
-      <c r="G7">
-        <v>14.2</v>
-      </c>
-      <c r="H7">
-        <v>17.9</v>
-      </c>
-      <c r="I7">
-        <v>18.5</v>
-      </c>
-      <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7">
-        <v>0.8</v>
-      </c>
       <c r="L7">
-        <v>42.8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1774,34 +1777,34 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="D8">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="E8">
-        <v>8.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="F8">
-        <v>12.9</v>
+        <v>12.5</v>
       </c>
       <c r="G8">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="H8">
-        <v>16.3</v>
+        <v>17.6</v>
       </c>
       <c r="I8">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="J8">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
       <c r="K8">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="L8">
-        <v>42.4</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1812,34 +1815,34 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D9">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="E9">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="F9">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="G9">
-        <v>17.3</v>
+        <v>14.8</v>
       </c>
       <c r="H9">
-        <v>19.5</v>
+        <v>18.2</v>
       </c>
       <c r="I9">
-        <v>20.9</v>
+        <v>23.7</v>
       </c>
       <c r="J9">
-        <v>23.4</v>
+        <v>24.6</v>
       </c>
       <c r="K9">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="L9">
-        <v>35.3</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1853,31 +1856,31 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="E10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F10">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="G10">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="H10">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="I10">
-        <v>22.7</v>
+        <v>25</v>
       </c>
       <c r="J10">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="K10">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L10">
-        <v>35.1</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1903,16 +1906,16 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="J11">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="K11">
-        <v>97.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1950,7 +1953,7 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1958,13 +1961,13 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>95.7</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="C3">
         <v>100</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1972,13 +1975,13 @@
         <v>0</v>
       </c>
       <c r="B4">
-        <v>87.09999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="C4">
-        <v>95.89999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="D4">
-        <v>96.5</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1986,13 +1989,13 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>98.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="C5">
-        <v>86.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D5">
-        <v>87.5</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2000,13 +2003,13 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>96.8</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="C6">
-        <v>69.8</v>
+        <v>68</v>
       </c>
       <c r="D6">
-        <v>65.5</v>
+        <v>65.10000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2014,13 +2017,13 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>48.5</v>
+        <v>47.7</v>
       </c>
       <c r="D7">
-        <v>44.2</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2028,13 +2031,13 @@
         <v>3</v>
       </c>
       <c r="B8">
-        <v>72.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="C8">
-        <v>40.6</v>
+        <v>38.6</v>
       </c>
       <c r="D8">
-        <v>40.7</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2042,13 +2045,13 @@
         <v>4</v>
       </c>
       <c r="B9">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="C9">
-        <v>24.5</v>
+        <v>25.6</v>
       </c>
       <c r="D9">
-        <v>33.2</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2056,10 +2059,10 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="C10">
-        <v>33.90000000000001</v>
+        <v>34.9</v>
       </c>
       <c r="D10">
         <v>32.4</v>
@@ -2470,7 +2473,7 @@
         <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2499,7 +2502,7 @@
         <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2519,7 +2522,7 @@
         <v>236.58</v>
       </c>
       <c r="F4">
-        <v>96.2</v>
+        <v>96.5</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2528,7 +2531,7 @@
         <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2548,16 +2551,16 @@
         <v>239.04</v>
       </c>
       <c r="F5">
-        <v>83.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="s">
         <v>64</v>
       </c>
       <c r="I5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2577,16 +2580,16 @@
         <v>210.08</v>
       </c>
       <c r="F6">
-        <v>64.60000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G6">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="s">
         <v>65</v>
       </c>
       <c r="I6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2606,16 +2609,16 @@
         <v>202.6</v>
       </c>
       <c r="F7">
-        <v>42.8</v>
+        <v>47</v>
       </c>
       <c r="G7">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H7" t="s">
         <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2635,16 +2638,16 @@
         <v>207.44</v>
       </c>
       <c r="F8">
-        <v>42.4</v>
+        <v>39.1</v>
       </c>
       <c r="G8">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="H8" t="s">
         <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2664,16 +2667,16 @@
         <v>207.1</v>
       </c>
       <c r="F9">
-        <v>35.3</v>
+        <v>33.1</v>
       </c>
       <c r="G9">
-        <v>0.8999999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="H9" t="s">
         <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2693,16 +2696,16 @@
         <v>209.2</v>
       </c>
       <c r="F10">
-        <v>35.09999999999999</v>
+        <v>32.8</v>
       </c>
       <c r="G10">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2725,13 +2728,13 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>97.3</v>
+        <v>96.89999999999999</v>
       </c>
       <c r="H11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2749,16 +2752,16 @@
         <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2778,7 +2781,7 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2798,7 +2801,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2818,7 +2821,7 @@
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2838,7 +2841,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2858,7 +2861,7 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2878,7 +2881,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2898,7 +2901,7 @@
         <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2918,7 +2921,7 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2938,7 +2941,7 @@
         <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2958,7 +2961,7 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2973,13 +2976,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2993,7 +2996,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3007,7 +3010,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3021,7 +3024,7 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3035,7 +3038,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3049,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3063,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3077,7 +3080,7 @@
         <v>-2</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3091,7 +3094,7 @@
         <v>-2</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3105,7 +3108,7 @@
         <v>-4</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3119,7 +3122,7 @@
         <v>-4</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Operators Football League 2026.xlsx
+++ b/data/leagues/Operators Football League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="104">
   <si>
     <t>Junya Ettlinger's First Team</t>
   </si>
@@ -55,13 +55,16 @@
     <t>Hall Pass</t>
   </si>
   <si>
-    <t>1-1-0</t>
-  </si>
-  <si>
-    <t>2-0-0</t>
-  </si>
-  <si>
-    <t>0-2-0</t>
+    <t>2-1-0</t>
+  </si>
+  <si>
+    <t>1-2-0</t>
+  </si>
+  <si>
+    <t>3-0-0</t>
+  </si>
+  <si>
+    <t>0-3-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -124,6 +127,9 @@
     <t>Week_3</t>
   </si>
   <si>
+    <t>Week_4</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -145,36 +151,36 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Julie Williston</t>
+  </si>
+  <si>
+    <t>Casey Reid</t>
+  </si>
+  <si>
     <t>Rachel Hall</t>
   </si>
   <si>
-    <t>Julie Williston</t>
+    <t>Jessica McNally</t>
   </si>
   <si>
     <t>Haley Toadvine</t>
   </si>
   <si>
-    <t>Casey Reid</t>
+    <t>Ava Patterson</t>
+  </si>
+  <si>
+    <t>Katie  Kush</t>
   </si>
   <si>
     <t>Carly Foster</t>
   </si>
   <si>
-    <t>Jessica McNally</t>
-  </si>
-  <si>
     <t>Morgan Herber</t>
   </si>
   <si>
-    <t>Katie  Kush</t>
-  </si>
-  <si>
     <t>Lauren Ettlinger</t>
   </si>
   <si>
-    <t>Ava Patterson</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -199,61 +205,70 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>10.9-3.0-0.1</t>
-  </si>
-  <si>
-    <t>11.7-2.2-0.1</t>
-  </si>
-  <si>
-    <t>8.5-5.4-0.1</t>
-  </si>
-  <si>
-    <t>7.5-6.4-0.1</t>
-  </si>
-  <si>
-    <t>6.9-7.0-0.1</t>
-  </si>
-  <si>
-    <t>6.1-7.8-0.1</t>
-  </si>
-  <si>
-    <t>5.6-8.3-0.1</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>12.0-1.9-0.1</t>
+  </si>
+  <si>
+    <t>10.4-3.5-0.1</t>
+  </si>
+  <si>
+    <t>9.1-4.8-0.1</t>
+  </si>
+  <si>
+    <t>8.0-5.9-0.1</t>
+  </si>
+  <si>
+    <t>7.4-6.4-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.0-0.1</t>
   </si>
   <si>
     <t>5.4-8.4-0.1</t>
   </si>
   <si>
-    <t>5.5-8.4-0.1</t>
-  </si>
-  <si>
-    <t>1.3-12.6-0.1</t>
+    <t>5.4-8.5-0.1</t>
+  </si>
+  <si>
+    <t>4.1-9.8-0.1</t>
+  </si>
+  <si>
+    <t>1.8-12.1-0.1</t>
+  </si>
+  <si>
+    <t>12-2</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
-    <t>12-2</t>
-  </si>
-  <si>
     <t>9-5</t>
   </si>
   <si>
-    <t>7-7</t>
+    <t>8-6</t>
   </si>
   <si>
     <t>6-8</t>
   </si>
   <si>
-    <t>1-13</t>
+    <t>5-9</t>
+  </si>
+  <si>
+    <t>4-10</t>
+  </si>
+  <si>
+    <t>2-12</t>
   </si>
   <si>
     <t>Owners</t>
@@ -265,31 +280,40 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>↑1</t>
   </si>
   <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↓3</t>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↓4</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↓2</t>
   </si>
   <si>
     <t>↓1</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↓2</t>
+    <t>↓6</t>
   </si>
   <si>
     <t>Week 1</t>
   </si>
   <si>
     <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
   </si>
   <si>
     <t>Week</t>
@@ -711,31 +735,31 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
-      </c>
       <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
-        <v>11</v>
-      </c>
       <c r="K2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -743,34 +767,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" t="s">
-        <v>11</v>
-      </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -778,34 +802,34 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -813,16 +837,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
@@ -834,7 +858,7 @@
         <v>10</v>
       </c>
       <c r="I5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J5" t="s">
         <v>10</v>
@@ -848,34 +872,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" t="s">
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -886,31 +910,31 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" t="s">
         <v>12</v>
       </c>
-      <c r="G7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" t="s">
-        <v>11</v>
-      </c>
       <c r="I7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" t="s">
         <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -918,34 +942,34 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
         <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -953,34 +977,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -988,34 +1012,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1026,25 +1050,25 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s">
         <v>12</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" t="s">
-        <v>11</v>
-      </c>
       <c r="I11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J11" t="s">
         <v>10</v>
@@ -1060,30 +1084,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1136,6 +1160,58 @@
       </c>
       <c r="H3" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1150,13 +1226,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1167,10 +1243,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1181,10 +1257,10 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1192,13 +1268,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1206,13 +1282,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1220,13 +1296,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1234,13 +1310,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1248,10 +1324,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1262,10 +1338,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1279,10 +1355,10 @@
         <v>8</v>
       </c>
       <c r="C10">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1293,10 +1369,10 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1311,16 +1387,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1331,13 +1407,13 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="D2">
-        <v>-0.2</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1348,13 +1424,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="D3">
-        <v>-0.2</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1362,13 +1438,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="D4">
-        <v>0.3999999999999999</v>
+        <v>-0.2</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1379,13 +1455,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="D5">
-        <v>0.1000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1396,16 +1472,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="D6">
-        <v>-0.09999999999999998</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1413,16 +1489,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="D7">
-        <v>-0.09999999999999998</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1430,16 +1506,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="D8">
-        <v>-0.2</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1447,16 +1523,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1464,16 +1540,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D10">
-        <v>0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1484,13 +1560,13 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1505,40 +1581,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1546,19 +1622,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>23.9</v>
+        <v>80.3</v>
       </c>
       <c r="C2">
-        <v>58.8</v>
+        <v>16.1</v>
       </c>
       <c r="D2">
-        <v>14.1</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="F2">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1567,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1576,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1584,25 +1660,25 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>71.3</v>
+        <v>15.7</v>
       </c>
       <c r="C3">
-        <v>24.3</v>
+        <v>49.9</v>
       </c>
       <c r="D3">
-        <v>3.2</v>
+        <v>21.5</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="F3">
-        <v>0.1</v>
+        <v>3.6</v>
       </c>
       <c r="G3">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1614,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>100</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1622,227 +1698,227 @@
         <v>0</v>
       </c>
       <c r="B4">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="C4">
-        <v>8.1</v>
+        <v>20.6</v>
       </c>
       <c r="D4">
-        <v>38.9</v>
+        <v>36.8</v>
       </c>
       <c r="E4">
-        <v>27.2</v>
+        <v>23.7</v>
       </c>
       <c r="F4">
-        <v>13.2</v>
+        <v>10.3</v>
       </c>
       <c r="G4">
-        <v>6.9</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="I4">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>96.5</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="C5">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="D5">
-        <v>19.8</v>
+        <v>22.4</v>
       </c>
       <c r="E5">
-        <v>26.8</v>
+        <v>30.2</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>21.9</v>
       </c>
       <c r="G5">
-        <v>13.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="I5">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J5">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>87.09999999999999</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>0.5</v>
       </c>
       <c r="C6">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="D6">
-        <v>12.8</v>
+        <v>11.6</v>
       </c>
       <c r="E6">
-        <v>14.9</v>
+        <v>23.9</v>
       </c>
       <c r="F6">
-        <v>19.9</v>
+        <v>31.1</v>
       </c>
       <c r="G6">
-        <v>14.6</v>
+        <v>15.4</v>
       </c>
       <c r="H6">
-        <v>13.6</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
-        <v>11.2</v>
+        <v>4.2</v>
       </c>
       <c r="J6">
-        <v>10.7</v>
+        <v>0.8</v>
       </c>
       <c r="K6">
         <v>0.1</v>
       </c>
       <c r="L6">
-        <v>64.40000000000001</v>
+        <v>86.8</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B7">
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="D7">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="E7">
-        <v>9.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>12.9</v>
+        <v>11.1</v>
       </c>
       <c r="G7">
-        <v>17.8</v>
+        <v>21.2</v>
       </c>
       <c r="H7">
-        <v>18</v>
+        <v>25.2</v>
       </c>
       <c r="I7">
-        <v>16.5</v>
+        <v>20.3</v>
       </c>
       <c r="J7">
-        <v>17.9</v>
+        <v>12.2</v>
       </c>
       <c r="K7">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>47</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0.2</v>
+      </c>
+      <c r="D8">
+        <v>0.9</v>
+      </c>
+      <c r="E8">
         <v>3</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0.3</v>
-      </c>
-      <c r="D8">
-        <v>2.4</v>
-      </c>
-      <c r="E8">
-        <v>7.2</v>
-      </c>
       <c r="F8">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>16.7</v>
+        <v>24.5</v>
       </c>
       <c r="H8">
-        <v>17.6</v>
+        <v>25.2</v>
       </c>
       <c r="I8">
-        <v>18.9</v>
+        <v>23</v>
       </c>
       <c r="J8">
-        <v>22.7</v>
+        <v>12.1</v>
       </c>
       <c r="K8">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="L8">
-        <v>39.1</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D9">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="F9">
-        <v>11.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G9">
-        <v>14.8</v>
+        <v>19</v>
       </c>
       <c r="H9">
-        <v>18.2</v>
+        <v>23.5</v>
       </c>
       <c r="I9">
-        <v>23.7</v>
+        <v>25.7</v>
       </c>
       <c r="J9">
-        <v>24.6</v>
+        <v>14.5</v>
       </c>
       <c r="K9">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="L9">
-        <v>33.1</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1856,31 +1932,31 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="F10">
-        <v>10.9</v>
+        <v>2.3</v>
       </c>
       <c r="G10">
-        <v>15.6</v>
+        <v>5.6</v>
       </c>
       <c r="H10">
-        <v>23.1</v>
+        <v>11.7</v>
       </c>
       <c r="I10">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J10">
-        <v>18.8</v>
+        <v>49.6</v>
       </c>
       <c r="K10">
-        <v>0.3</v>
+        <v>8.4</v>
       </c>
       <c r="L10">
-        <v>32.8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1906,16 +1982,16 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I11">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J11">
-        <v>2.8</v>
+        <v>10.3</v>
       </c>
       <c r="K11">
-        <v>96.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1928,147 +2004,177 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>98.40000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2">
-        <v>99.90000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>95.19999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="C3">
         <v>100</v>
       </c>
       <c r="D3">
-        <v>99.90000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>99.7</v>
+      </c>
+      <c r="E3">
+        <v>99.59999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4">
-        <v>86.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="C4">
-        <v>95.8</v>
+        <v>97.5</v>
       </c>
       <c r="D4">
-        <v>94.8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="E4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>79.2</v>
+      </c>
+      <c r="C5">
+        <v>37.1</v>
+      </c>
+      <c r="D5">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="E5">
+        <v>92.60000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>0.2</v>
+      </c>
+      <c r="C6">
+        <v>33.90000000000001</v>
+      </c>
+      <c r="D6">
+        <v>88.5</v>
+      </c>
+      <c r="E6">
+        <v>87.09999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="C7">
+        <v>68.89999999999999</v>
+      </c>
+      <c r="D7">
+        <v>40.9</v>
+      </c>
+      <c r="E7">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>33.8</v>
+      </c>
+      <c r="D8">
+        <v>39</v>
+      </c>
+      <c r="E8">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5">
-        <v>98</v>
-      </c>
-      <c r="C5">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="D5">
-        <v>85.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>96.89999999999999</v>
-      </c>
-      <c r="C6">
-        <v>68</v>
-      </c>
-      <c r="D6">
-        <v>65.10000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>47.7</v>
-      </c>
-      <c r="D7">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="C8">
-        <v>38.6</v>
-      </c>
-      <c r="D8">
-        <v>43.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="B9">
+        <v>99.7</v>
+      </c>
+      <c r="C9">
+        <v>94</v>
+      </c>
+      <c r="D9">
+        <v>28.7</v>
+      </c>
+      <c r="E9">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B9">
-        <v>47.2</v>
-      </c>
-      <c r="C9">
-        <v>25.6</v>
-      </c>
-      <c r="D9">
-        <v>32.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="B10">
+        <v>33.5</v>
+      </c>
+      <c r="C10">
+        <v>34.8</v>
+      </c>
+      <c r="D10">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>4.2</v>
-      </c>
-      <c r="C10">
-        <v>34.9</v>
-      </c>
-      <c r="D10">
-        <v>32.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10">
+        <v>8.699999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
@@ -2080,6 +2186,9 @@
       </c>
       <c r="D11">
         <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -2094,28 +2203,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2123,28 +2232,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>103.55</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>112.78</v>
+        <v>110.93</v>
       </c>
       <c r="G2">
-        <v>0.583</v>
+        <v>0.515</v>
       </c>
       <c r="H2">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2152,28 +2261,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>104.6</v>
+        <v>83.77</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>112.11</v>
+        <v>111.9</v>
       </c>
       <c r="G3">
-        <v>0.542</v>
+        <v>0.515</v>
       </c>
       <c r="H3">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2181,28 +2290,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4">
-        <v>119.52</v>
+        <v>112.86</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>112.86</v>
+        <v>112.31</v>
       </c>
       <c r="G4">
-        <v>0.583</v>
+        <v>0.576</v>
       </c>
       <c r="H4">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2210,28 +2319,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>75.63</v>
+        <v>105.85</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>112.09</v>
+        <v>112.64</v>
       </c>
       <c r="G5">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="H5">
         <v>0.2</v>
       </c>
       <c r="I5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2239,28 +2348,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6">
-        <v>103.72</v>
+        <v>104.37</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>105.99</v>
+        <v>111.88</v>
       </c>
       <c r="G6">
-        <v>0.5</v>
+        <v>0.576</v>
       </c>
       <c r="H6">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2268,28 +2377,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>101.3</v>
+        <v>121.98</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>110.72</v>
+        <v>108.15</v>
       </c>
       <c r="G7">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="H7">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2297,28 +2406,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8">
-        <v>118.29</v>
+        <v>131.95</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>106.26</v>
+        <v>107.38</v>
       </c>
       <c r="G8">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="H8">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2326,28 +2435,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9">
-        <v>129.03</v>
+        <v>118.53</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9">
-        <v>107.41</v>
+        <v>105.95</v>
       </c>
       <c r="G9">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="H9">
         <v>-0.5</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2355,28 +2464,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10">
-        <v>105.04</v>
+        <v>118.7</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10">
-        <v>106.04</v>
+        <v>106.79</v>
       </c>
       <c r="G10">
-        <v>0.417</v>
+        <v>0.455</v>
       </c>
       <c r="H10">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2384,28 +2493,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11">
-        <v>132.94</v>
+        <v>101.77</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11">
-        <v>107.36</v>
+        <v>106.45</v>
       </c>
       <c r="G11">
-        <v>0.458</v>
+        <v>0.455</v>
       </c>
       <c r="H11">
-        <v>-0.8</v>
+        <v>-1.5</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2420,31 +2529,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2452,28 +2561,28 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>129.03</v>
+        <v>131.9533333333333</v>
       </c>
       <c r="E2">
-        <v>258.06</v>
+        <v>395.86</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2481,28 +2590,28 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>132.94</v>
+        <v>121.98</v>
       </c>
       <c r="E3">
-        <v>265.88</v>
+        <v>365.94</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2510,173 +2619,173 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>118.29</v>
+        <v>118.7</v>
       </c>
       <c r="E4">
-        <v>236.58</v>
+        <v>356.1</v>
       </c>
       <c r="F4">
-        <v>96.5</v>
+        <v>98.3</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D5">
-        <v>119.52</v>
+        <v>118.5266666666667</v>
       </c>
       <c r="E5">
-        <v>239.04</v>
+        <v>355.58</v>
       </c>
       <c r="F5">
-        <v>87.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D6">
-        <v>105.04</v>
+        <v>112.86</v>
       </c>
       <c r="E6">
-        <v>210.08</v>
+        <v>338.58</v>
       </c>
       <c r="F6">
-        <v>64.40000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="G6">
         <v>0.1</v>
       </c>
       <c r="H6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7">
-        <v>101.3</v>
+        <v>101.7733333333333</v>
       </c>
       <c r="E7">
-        <v>202.6</v>
+        <v>305.32</v>
       </c>
       <c r="F7">
-        <v>47</v>
+        <v>41.3</v>
       </c>
       <c r="G7">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8">
-        <v>103.72</v>
+        <v>105.8466666666666</v>
       </c>
       <c r="E8">
-        <v>207.44</v>
+        <v>317.54</v>
       </c>
       <c r="F8">
-        <v>39.1</v>
+        <v>38.6</v>
       </c>
       <c r="G8">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>103.55</v>
+        <v>104.3733333333333</v>
       </c>
       <c r="E9">
-        <v>207.1</v>
+        <v>313.12</v>
       </c>
       <c r="F9">
-        <v>33.1</v>
+        <v>33.8</v>
       </c>
       <c r="G9">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I9" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2684,28 +2793,28 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10">
-        <v>104.6</v>
+        <v>94.59999999999998</v>
       </c>
       <c r="E10">
-        <v>209.2</v>
+        <v>283.8</v>
       </c>
       <c r="F10">
-        <v>32.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G10">
-        <v>0.3</v>
+        <v>8.4</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2713,28 +2822,28 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>75.63</v>
+        <v>83.76666666666667</v>
       </c>
       <c r="E11">
-        <v>151.26</v>
+        <v>251.3</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>96.89999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="H11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2749,19 +2858,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2769,19 +2878,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2789,19 +2898,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2809,19 +2918,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2829,19 +2938,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2852,16 +2961,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2869,19 +2978,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2889,19 +2998,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
         <v>44</v>
       </c>
       <c r="D8">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2909,19 +3018,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D9">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2935,13 +3044,13 @@
         <v>43</v>
       </c>
       <c r="D10">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2949,19 +3058,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2971,77 +3080,92 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -3051,53 +3175,65 @@
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>-2</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="C8">
-        <v>-2</v>
-      </c>
-      <c r="D8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>-4</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B9">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>-2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -3107,22 +3243,28 @@
       <c r="C10">
         <v>-4</v>
       </c>
-      <c r="D10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="D10">
+        <v>-5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B11">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="C11">
-        <v>-4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>85</v>
+        <v>-2</v>
+      </c>
+      <c r="D11">
+        <v>-8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Operators Football League 2026.xlsx
+++ b/data/leagues/Operators Football League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="104">
   <si>
     <t>Junya Ettlinger's First Team</t>
   </si>
@@ -55,16 +55,19 @@
     <t>Hall Pass</t>
   </si>
   <si>
-    <t>2-1-0</t>
-  </si>
-  <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>3-0-0</t>
-  </si>
-  <si>
-    <t>0-3-0</t>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>4-0-0</t>
+  </si>
+  <si>
+    <t>0-4-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -130,6 +133,9 @@
     <t>Week_4</t>
   </si>
   <si>
+    <t>Week_5</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -154,13 +160,19 @@
     <t>Julie Williston</t>
   </si>
   <si>
+    <t>Jessica McNally</t>
+  </si>
+  <si>
+    <t>Morgan Herber</t>
+  </si>
+  <si>
+    <t>Rachel Hall</t>
+  </si>
+  <si>
     <t>Casey Reid</t>
   </si>
   <si>
-    <t>Rachel Hall</t>
-  </si>
-  <si>
-    <t>Jessica McNally</t>
+    <t>Carly Foster</t>
   </si>
   <si>
     <t>Haley Toadvine</t>
@@ -172,12 +184,6 @@
     <t>Katie  Kush</t>
   </si>
   <si>
-    <t>Carly Foster</t>
-  </si>
-  <si>
-    <t>Morgan Herber</t>
-  </si>
-  <si>
     <t>Lauren Ettlinger</t>
   </si>
   <si>
@@ -205,70 +211,61 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>12.0-1.9-0.1</t>
-  </si>
-  <si>
-    <t>10.4-3.5-0.1</t>
-  </si>
-  <si>
-    <t>9.1-4.8-0.1</t>
-  </si>
-  <si>
-    <t>8.0-5.9-0.1</t>
-  </si>
-  <si>
-    <t>7.4-6.4-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.0-0.1</t>
-  </si>
-  <si>
-    <t>5.4-8.4-0.1</t>
-  </si>
-  <si>
-    <t>5.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>4.1-9.8-0.1</t>
-  </si>
-  <si>
-    <t>1.8-12.1-0.1</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>12.1-1.8-0.1</t>
+  </si>
+  <si>
+    <t>9.8-4.1-0.1</t>
+  </si>
+  <si>
+    <t>9.7-4.2-0.1</t>
+  </si>
+  <si>
+    <t>7.7-6.1-0.1</t>
+  </si>
+  <si>
+    <t>7.1-6.8-0.2</t>
+  </si>
+  <si>
+    <t>6.8-7.1-0.1</t>
+  </si>
+  <si>
+    <t>4.4-9.5-0.1</t>
+  </si>
+  <si>
+    <t>4.0-9.9-0.1</t>
+  </si>
+  <si>
+    <t>3.4-10.5-0.1</t>
   </si>
   <si>
     <t>12-2</t>
   </si>
   <si>
-    <t>11-3</t>
-  </si>
-  <si>
-    <t>9-5</t>
+    <t>10-4</t>
   </si>
   <si>
     <t>8-6</t>
   </si>
   <si>
-    <t>6-8</t>
-  </si>
-  <si>
-    <t>5-9</t>
+    <t>7-7</t>
   </si>
   <si>
     <t>4-10</t>
   </si>
   <si>
-    <t>2-12</t>
+    <t>3-11</t>
   </si>
   <si>
     <t>Owners</t>
@@ -280,33 +277,33 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↓4</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↑5</t>
+    <t>↓3</t>
+  </si>
+  <si>
+    <t>↓6</t>
   </si>
   <si>
     <t>↓2</t>
   </si>
   <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↓6</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -314,6 +311,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -735,31 +735,31 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
       <c r="I2" t="s">
         <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -770,31 +770,31 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -805,7 +805,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -814,7 +814,7 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
@@ -840,31 +840,31 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
         <v>11</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -872,34 +872,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -910,31 +910,31 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -942,34 +942,34 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s">
         <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -977,34 +977,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
       </c>
       <c r="I9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J9" t="s">
         <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1012,34 +1012,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" t="s">
         <v>11</v>
       </c>
       <c r="J10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1050,31 +1050,31 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
         <v>10</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I11" t="s">
         <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1084,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1141,25 +1141,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>-4</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
       <c r="H3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1170,22 +1170,22 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1193,25 +1193,51 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5">
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>2</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>3</v>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1226,13 +1252,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1240,13 +1266,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1254,13 +1280,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1268,13 +1294,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1285,7 +1311,7 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -1296,13 +1322,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1310,10 +1336,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -1324,13 +1350,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1338,10 +1364,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1352,13 +1378,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1369,10 +1395,10 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1387,16 +1413,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1407,13 +1433,13 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="D2">
-        <v>-0.2999999999999998</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1421,16 +1447,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="D3">
-        <v>-0.7000000000000002</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1438,13 +1464,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="D4">
-        <v>-0.2</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1455,16 +1481,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="D5">
-        <v>-0.3</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1472,13 +1498,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="D6">
-        <v>0.6000000000000001</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -1489,13 +1515,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7">
         <v>2</v>
       </c>
-      <c r="C7">
-        <v>1.4</v>
-      </c>
       <c r="D7">
-        <v>0.3999999999999999</v>
+        <v>0</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -1509,13 +1535,13 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="D8">
-        <v>0.3999999999999999</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1523,16 +1549,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1540,16 +1566,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D10">
-        <v>-0.2</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1557,16 +1583,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="D11">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1581,40 +1607,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1622,16 +1648,16 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>80.3</v>
+        <v>85.2</v>
       </c>
       <c r="C2">
-        <v>16.1</v>
+        <v>12.4</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="E2">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1643,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1652,33 +1678,33 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B3">
-        <v>15.7</v>
+        <v>7.1</v>
       </c>
       <c r="C3">
-        <v>49.9</v>
+        <v>42.9</v>
       </c>
       <c r="D3">
-        <v>21.5</v>
+        <v>33.5</v>
       </c>
       <c r="E3">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="F3">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G3">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="H3">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1690,45 +1716,45 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>2.9</v>
+        <v>7.4</v>
       </c>
       <c r="C4">
-        <v>20.6</v>
+        <v>36.3</v>
       </c>
       <c r="D4">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="E4">
-        <v>23.7</v>
+        <v>13.6</v>
       </c>
       <c r="F4">
-        <v>10.3</v>
+        <v>4.4</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="H4">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="I4">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J4">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>98.3</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1736,37 +1762,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="C5">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="D5">
-        <v>22.4</v>
+        <v>13.9</v>
       </c>
       <c r="E5">
-        <v>30.2</v>
+        <v>34.4</v>
       </c>
       <c r="F5">
-        <v>21.9</v>
+        <v>24.8</v>
       </c>
       <c r="G5">
-        <v>9.699999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="H5">
         <v>4</v>
       </c>
       <c r="I5">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J5">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>93.2</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1774,75 +1800,75 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="D6">
-        <v>11.6</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>23.9</v>
+        <v>21.5</v>
       </c>
       <c r="F6">
-        <v>31.1</v>
+        <v>33.3</v>
       </c>
       <c r="G6">
-        <v>15.4</v>
+        <v>20.6</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J6">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="K6">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L6">
-        <v>86.8</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="D7">
-        <v>1.8</v>
+        <v>5.3</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>16.2</v>
       </c>
       <c r="F7">
-        <v>11.1</v>
+        <v>26.1</v>
       </c>
       <c r="G7">
-        <v>21.2</v>
+        <v>33.1</v>
       </c>
       <c r="H7">
-        <v>25.2</v>
+        <v>10.8</v>
       </c>
       <c r="I7">
-        <v>20.3</v>
+        <v>4.4</v>
       </c>
       <c r="J7">
-        <v>12.2</v>
+        <v>1.9</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="L7">
-        <v>41.3</v>
+        <v>82.2</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1853,77 +1879,77 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="E8">
+        <v>1.1</v>
+      </c>
+      <c r="F8">
         <v>3</v>
       </c>
-      <c r="F8">
-        <v>10</v>
-      </c>
       <c r="G8">
-        <v>24.5</v>
+        <v>10.3</v>
       </c>
       <c r="H8">
-        <v>25.2</v>
+        <v>28.7</v>
       </c>
       <c r="I8">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="J8">
-        <v>12.1</v>
+        <v>22.6</v>
       </c>
       <c r="K8">
-        <v>1.1</v>
+        <v>11.5</v>
       </c>
       <c r="L8">
-        <v>38.6</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
         <v>0.3</v>
       </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
       <c r="E9">
+        <v>0.9</v>
+      </c>
+      <c r="F9">
         <v>2.8</v>
       </c>
-      <c r="F9">
-        <v>9.699999999999999</v>
-      </c>
       <c r="G9">
-        <v>19</v>
+        <v>8.9</v>
       </c>
       <c r="H9">
-        <v>23.5</v>
+        <v>22.9</v>
       </c>
       <c r="I9">
-        <v>25.7</v>
+        <v>27.1</v>
       </c>
       <c r="J9">
-        <v>14.5</v>
+        <v>20.8</v>
       </c>
       <c r="K9">
-        <v>2.5</v>
+        <v>16.3</v>
       </c>
       <c r="L9">
-        <v>33.8</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1932,36 +1958,36 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E10">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F10">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G10">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H10">
-        <v>11.7</v>
+        <v>14.6</v>
       </c>
       <c r="I10">
-        <v>22</v>
+        <v>25.9</v>
       </c>
       <c r="J10">
-        <v>49.6</v>
+        <v>27.2</v>
       </c>
       <c r="K10">
-        <v>8.4</v>
+        <v>24.3</v>
       </c>
       <c r="L10">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1976,25 +2002,25 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="H11">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="I11">
-        <v>2.1</v>
+        <v>14.5</v>
       </c>
       <c r="J11">
-        <v>10.3</v>
+        <v>25.8</v>
       </c>
       <c r="K11">
-        <v>86.90000000000001</v>
+        <v>47</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -2004,29 +2030,32 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2037,93 +2066,111 @@
       <c r="E2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>91.2</v>
+      </c>
+      <c r="C3">
+        <v>97.7</v>
+      </c>
+      <c r="D3">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3">
-        <v>98.5</v>
-      </c>
-      <c r="C3">
+      <c r="B4">
+        <v>98</v>
+      </c>
+      <c r="C4">
         <v>100</v>
       </c>
-      <c r="D3">
-        <v>99.7</v>
-      </c>
-      <c r="E3">
+      <c r="D4">
+        <v>99.8</v>
+      </c>
+      <c r="E4">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="F4">
         <v>99.59999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="C4">
-        <v>97.5</v>
-      </c>
-      <c r="D4">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="E4">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>79.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="C5">
-        <v>37.1</v>
+        <v>38.9</v>
       </c>
       <c r="D5">
+        <v>95.39999999999999</v>
+      </c>
+      <c r="E5">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="F5">
         <v>94.59999999999999</v>
       </c>
-      <c r="E5">
-        <v>92.60000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.2</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="C6">
-        <v>33.90000000000001</v>
+        <v>27.9</v>
       </c>
       <c r="D6">
-        <v>88.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="E6">
-        <v>87.09999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>85.2</v>
+      </c>
+      <c r="F6">
+        <v>89.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7">
-        <v>98.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="C7">
-        <v>68.89999999999999</v>
+        <v>92.80000000000001</v>
       </c>
       <c r="D7">
-        <v>40.9</v>
+        <v>30.1</v>
       </c>
       <c r="E7">
-        <v>40.6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>81.39999999999999</v>
+      </c>
+      <c r="F7">
+        <v>80.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -2131,64 +2178,76 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>33.8</v>
+        <v>36.8</v>
       </c>
       <c r="D8">
-        <v>39</v>
+        <v>41.5</v>
       </c>
       <c r="E8">
-        <v>38.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>15</v>
+      </c>
+      <c r="F8">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9">
-        <v>99.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="C9">
-        <v>94</v>
+        <v>70.19999999999999</v>
       </c>
       <c r="D9">
-        <v>28.7</v>
+        <v>41.3</v>
       </c>
       <c r="E9">
-        <v>33.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>13.6</v>
+      </c>
+      <c r="F9">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>8.9</v>
+      </c>
+      <c r="F10">
+        <v>7.399999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10">
-        <v>33.5</v>
-      </c>
-      <c r="C10">
-        <v>34.8</v>
-      </c>
-      <c r="D10">
-        <v>9</v>
-      </c>
-      <c r="E10">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="B11">
-        <v>0</v>
+        <v>35.09999999999999</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>35.7</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="E11">
-        <v>0.3</v>
+        <v>2.4</v>
+      </c>
+      <c r="F11">
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
@@ -2203,28 +2262,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2235,25 +2294,25 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>94.59999999999999</v>
+        <v>91.93000000000001</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>110.93</v>
+        <v>110.91</v>
       </c>
       <c r="G2">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2261,28 +2320,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>83.77</v>
+        <v>101.73</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>111.9</v>
+        <v>113.22</v>
       </c>
       <c r="G3">
-        <v>0.515</v>
+        <v>0.575</v>
       </c>
       <c r="H3">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2290,28 +2349,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>112.86</v>
+        <v>123.18</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>112.31</v>
+        <v>109.1</v>
       </c>
       <c r="G4">
-        <v>0.576</v>
+        <v>0.475</v>
       </c>
       <c r="H4">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2319,28 +2378,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5">
-        <v>105.85</v>
+        <v>113.43</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5">
-        <v>112.64</v>
+        <v>111.27</v>
       </c>
       <c r="G5">
-        <v>0.545</v>
+        <v>0.525</v>
       </c>
       <c r="H5">
         <v>0.2</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2348,28 +2407,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>104.37</v>
+        <v>96.2</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6">
-        <v>111.88</v>
+        <v>112.26</v>
       </c>
       <c r="G6">
-        <v>0.576</v>
+        <v>0.525</v>
       </c>
       <c r="H6">
         <v>0.1</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2377,28 +2436,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>121.98</v>
+        <v>115.36</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>108.15</v>
+        <v>108.43</v>
       </c>
       <c r="G7">
-        <v>0.455</v>
+        <v>0.475</v>
       </c>
       <c r="H7">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2406,28 +2465,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>131.95</v>
+        <v>110.76</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>107.38</v>
+        <v>111.59</v>
       </c>
       <c r="G8">
-        <v>0.455</v>
+        <v>0.525</v>
       </c>
       <c r="H8">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2435,28 +2494,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>118.53</v>
+        <v>122.72</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9">
-        <v>105.95</v>
+        <v>109.42</v>
       </c>
       <c r="G9">
-        <v>0.455</v>
+        <v>0.475</v>
       </c>
       <c r="H9">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2464,28 +2523,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10">
-        <v>118.7</v>
+        <v>130.53</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>106.79</v>
+        <v>107.46</v>
       </c>
       <c r="G10">
-        <v>0.455</v>
+        <v>0.425</v>
       </c>
       <c r="H10">
-        <v>-0.9</v>
+        <v>-1.1</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2496,25 +2555,25 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11">
-        <v>101.77</v>
+        <v>97.59</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>106.45</v>
+        <v>109.78</v>
       </c>
       <c r="G11">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="H11">
-        <v>-1.5</v>
+        <v>-1.2</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2529,31 +2588,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2561,83 +2620,83 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>131.9533333333333</v>
+        <v>130.535</v>
       </c>
       <c r="E2">
-        <v>395.86</v>
+        <v>522.14</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D3">
-        <v>121.98</v>
+        <v>123.18</v>
       </c>
       <c r="E3">
-        <v>365.94</v>
+        <v>492.72</v>
       </c>
       <c r="F3">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D4">
-        <v>118.7</v>
+        <v>122.715</v>
       </c>
       <c r="E4">
-        <v>356.1</v>
+        <v>490.86</v>
       </c>
       <c r="F4">
-        <v>98.3</v>
+        <v>99.8</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I4" t="s">
         <v>76</v>
@@ -2648,25 +2707,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>118.5266666666667</v>
+        <v>115.365</v>
       </c>
       <c r="E5">
-        <v>355.58</v>
+        <v>461.46</v>
       </c>
       <c r="F5">
-        <v>93.2</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
         <v>77</v>
@@ -2677,54 +2736,54 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C6">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>112.86</v>
+        <v>113.425</v>
       </c>
       <c r="E6">
-        <v>338.58</v>
+        <v>453.7</v>
       </c>
       <c r="F6">
-        <v>86.8</v>
+        <v>85.8</v>
       </c>
       <c r="G6">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C7">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>101.7733333333333</v>
+        <v>110.76</v>
       </c>
       <c r="E7">
-        <v>305.32</v>
+        <v>443.04</v>
       </c>
       <c r="F7">
-        <v>41.3</v>
+        <v>82.19999999999999</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I7" t="s">
         <v>78</v>
@@ -2735,54 +2794,54 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C8">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D8">
-        <v>105.8466666666666</v>
+        <v>101.735</v>
       </c>
       <c r="E8">
-        <v>317.54</v>
+        <v>406.9399999999999</v>
       </c>
       <c r="F8">
-        <v>38.6</v>
+        <v>14.5</v>
       </c>
       <c r="G8">
-        <v>1.1</v>
+        <v>11.5</v>
       </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D9">
-        <v>104.3733333333333</v>
+        <v>97.595</v>
       </c>
       <c r="E9">
-        <v>313.12</v>
+        <v>390.38</v>
       </c>
       <c r="F9">
-        <v>33.8</v>
+        <v>12.9</v>
       </c>
       <c r="G9">
-        <v>2.5</v>
+        <v>16.3</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I9" t="s">
         <v>79</v>
@@ -2790,60 +2849,60 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C10">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D10">
-        <v>94.59999999999998</v>
+        <v>96.2</v>
       </c>
       <c r="E10">
-        <v>283.8</v>
+        <v>384.8</v>
       </c>
       <c r="F10">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="G10">
-        <v>8.4</v>
+        <v>24.3</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D11">
-        <v>83.76666666666667</v>
+        <v>91.93499999999999</v>
       </c>
       <c r="E11">
-        <v>251.3</v>
+        <v>367.74</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G11">
-        <v>86.90000000000001</v>
+        <v>47</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2858,19 +2917,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2881,16 +2940,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2898,19 +2957,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2918,19 +2977,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2938,19 +2997,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2958,19 +3017,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2978,10 +3037,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2998,16 +3057,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>90</v>
@@ -3018,16 +3077,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
         <v>91</v>
@@ -3041,16 +3100,16 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D10">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3061,16 +3120,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -3080,24 +3139,27 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -3110,130 +3172,154 @@
       <c r="D2">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3">
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
+      <c r="F5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>-6</v>
+      </c>
+      <c r="C7">
+        <v>-4</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>-2</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>-2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>-2</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>-6</v>
-      </c>
-      <c r="C8">
+      <c r="E9">
         <v>-4</v>
       </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -3246,11 +3332,14 @@
       <c r="D10">
         <v>-5</v>
       </c>
-      <c r="E10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="E10">
+        <v>-4</v>
+      </c>
+      <c r="F10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -3263,8 +3352,11 @@
       <c r="D11">
         <v>-8</v>
       </c>
-      <c r="E11" t="s">
-        <v>93</v>
+      <c r="E11">
+        <v>-10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Operators Football League 2026.xlsx
+++ b/data/leagues/Operators Football League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="107">
   <si>
     <t>Junya Ettlinger's First Team</t>
   </si>
@@ -55,19 +55,22 @@
     <t>Hall Pass</t>
   </si>
   <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
-    <t>4-0-0</t>
-  </si>
-  <si>
-    <t>0-4-0</t>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>4-1-0</t>
+  </si>
+  <si>
+    <t>1-4-0</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
+  </si>
+  <si>
+    <t>0-5-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -136,6 +139,9 @@
     <t>Week_5</t>
   </si>
   <si>
+    <t>Week_6</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -160,33 +166,33 @@
     <t>Julie Williston</t>
   </si>
   <si>
+    <t>Casey Reid</t>
+  </si>
+  <si>
+    <t>Lauren Ettlinger</t>
+  </si>
+  <si>
+    <t>Carly Foster</t>
+  </si>
+  <si>
+    <t>Morgan Herber</t>
+  </si>
+  <si>
+    <t>Haley Toadvine</t>
+  </si>
+  <si>
     <t>Jessica McNally</t>
   </si>
   <si>
-    <t>Morgan Herber</t>
+    <t>Ava Patterson</t>
   </si>
   <si>
     <t>Rachel Hall</t>
   </si>
   <si>
-    <t>Casey Reid</t>
-  </si>
-  <si>
-    <t>Carly Foster</t>
-  </si>
-  <si>
-    <t>Haley Toadvine</t>
-  </si>
-  <si>
-    <t>Ava Patterson</t>
-  </si>
-  <si>
     <t>Katie  Kush</t>
   </si>
   <si>
-    <t>Lauren Ettlinger</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -211,49 +217,49 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>12.1-1.8-0.1</t>
-  </si>
-  <si>
-    <t>9.8-4.1-0.1</t>
-  </si>
-  <si>
-    <t>9.7-4.2-0.1</t>
-  </si>
-  <si>
-    <t>7.7-6.1-0.1</t>
-  </si>
-  <si>
-    <t>7.1-6.8-0.2</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>4.4-9.5-0.1</t>
-  </si>
-  <si>
-    <t>4.0-9.9-0.1</t>
-  </si>
-  <si>
-    <t>3.4-10.5-0.1</t>
-  </si>
-  <si>
-    <t>12-2</t>
-  </si>
-  <si>
-    <t>10-4</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>10.8-3.1-0.1</t>
+  </si>
+  <si>
+    <t>9.2-4.8-0.1</t>
+  </si>
+  <si>
+    <t>8.4-5.5-0.1</t>
+  </si>
+  <si>
+    <t>7.9-6.0-0.1</t>
+  </si>
+  <si>
+    <t>7.2-6.7-0.1</t>
+  </si>
+  <si>
+    <t>6.5-7.4-0.1</t>
+  </si>
+  <si>
+    <t>4.8-9.1-0.1</t>
+  </si>
+  <si>
+    <t>3.5-10.4-0.1</t>
+  </si>
+  <si>
+    <t>2.8-11.1-0.1</t>
+  </si>
+  <si>
+    <t>11-3</t>
+  </si>
+  <si>
+    <t>9-5</t>
   </si>
   <si>
     <t>8-6</t>
@@ -262,7 +268,7 @@
     <t>7-7</t>
   </si>
   <si>
-    <t>4-10</t>
+    <t>5-9</t>
   </si>
   <si>
     <t>3-11</t>
@@ -277,33 +283,33 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↑5</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↑1</t>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↑7</t>
+  </si>
+  <si>
+    <t>↑9</t>
   </si>
   <si>
     <t>↓1</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>↓3</t>
   </si>
   <si>
-    <t>↓6</t>
-  </si>
-  <si>
     <t>↓2</t>
   </si>
   <si>
+    <t>↓7</t>
+  </si>
+  <si>
+    <t>↓9</t>
+  </si>
+  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -314,6 +320,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -735,31 +744,31 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -770,31 +779,31 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
         <v>10</v>
       </c>
       <c r="K3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -802,19 +811,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
@@ -837,19 +846,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -858,13 +867,13 @@
         <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" t="s">
         <v>11</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -872,34 +881,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -907,34 +916,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" t="s">
-        <v>10</v>
-      </c>
       <c r="I7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J7" t="s">
         <v>11</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -942,34 +951,34 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J8" t="s">
         <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -977,34 +986,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
       </c>
       <c r="I9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J9" t="s">
         <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1012,25 +1021,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I10" t="s">
         <v>11</v>
@@ -1047,34 +1056,34 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" t="s">
         <v>12</v>
       </c>
-      <c r="G11" t="s">
-        <v>10</v>
-      </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1084,30 +1093,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1115,25 +1124,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1141,25 +1150,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>-4</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1167,25 +1176,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
       <c r="E4">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1193,16 +1202,16 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5">
         <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1211,7 +1220,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1238,6 +1247,32 @@
       </c>
       <c r="H6" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1252,13 +1287,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1269,10 +1304,10 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1283,10 +1318,10 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1294,13 +1329,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1311,10 +1346,10 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1322,13 +1357,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1339,10 +1374,10 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1350,13 +1385,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1364,10 +1399,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1378,13 +1413,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1392,13 +1427,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1413,16 +1448,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1433,13 +1468,13 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="D2">
-        <v>-0.6000000000000001</v>
+        <v>0.09999999999999964</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1447,13 +1482,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="D3">
-        <v>-0.2000000000000002</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1464,13 +1499,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="D4">
-        <v>-0.2000000000000002</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1481,16 +1516,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="D5">
-        <v>0.2000000000000002</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1498,16 +1533,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="D6">
-        <v>0.1000000000000001</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1518,13 +1553,13 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1535,13 +1570,13 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="D8">
-        <v>0.6000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1549,16 +1584,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="D9">
-        <v>0.2</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1566,16 +1601,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="D10">
-        <v>0.1000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1592,7 +1627,7 @@
         <v>-0.2</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1607,40 +1642,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1648,22 +1683,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>85.2</v>
+        <v>68.8</v>
       </c>
       <c r="C2">
-        <v>12.4</v>
+        <v>20.9</v>
       </c>
       <c r="D2">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="E2">
-        <v>0.2</v>
+        <v>3.2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1683,40 +1718,40 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>7.1</v>
+        <v>18.7</v>
       </c>
       <c r="C3">
-        <v>42.9</v>
+        <v>32.1</v>
       </c>
       <c r="D3">
-        <v>33.5</v>
+        <v>22.3</v>
       </c>
       <c r="E3">
-        <v>11.5</v>
+        <v>12.8</v>
       </c>
       <c r="F3">
-        <v>3.3</v>
+        <v>7.9</v>
       </c>
       <c r="G3">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="H3">
+        <v>1.5</v>
+      </c>
+      <c r="I3">
+        <v>0.3</v>
+      </c>
+      <c r="J3">
         <v>0.1</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.90000000000001</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1724,28 +1759,28 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="C4">
-        <v>36.3</v>
+        <v>16.2</v>
       </c>
       <c r="D4">
-        <v>36.6</v>
+        <v>21.3</v>
       </c>
       <c r="E4">
-        <v>13.6</v>
+        <v>21.4</v>
       </c>
       <c r="F4">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="G4">
-        <v>1.5</v>
+        <v>10.8</v>
       </c>
       <c r="H4">
-        <v>0.1</v>
+        <v>4.6</v>
       </c>
       <c r="I4">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1754,36 +1789,36 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>99.8</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>0.2</v>
+        <v>4.2</v>
       </c>
       <c r="C5">
-        <v>4.6</v>
+        <v>17.3</v>
       </c>
       <c r="D5">
-        <v>13.9</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>34.4</v>
+        <v>21.5</v>
       </c>
       <c r="F5">
-        <v>24.8</v>
+        <v>18.5</v>
       </c>
       <c r="G5">
-        <v>16.5</v>
+        <v>10.3</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="I5">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J5">
         <v>0.2</v>
@@ -1792,45 +1827,45 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>94.40000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="C6">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="D6">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>21.5</v>
+        <v>18.6</v>
       </c>
       <c r="F6">
-        <v>33.3</v>
+        <v>20.5</v>
       </c>
       <c r="G6">
-        <v>20.6</v>
+        <v>18.4</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="I6">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J6">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="K6">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L6">
-        <v>85.8</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1838,37 +1873,37 @@
         <v>2</v>
       </c>
       <c r="B7">
+        <v>0.7</v>
+      </c>
+      <c r="C7">
+        <v>2.5</v>
+      </c>
+      <c r="D7">
+        <v>6.9</v>
+      </c>
+      <c r="E7">
+        <v>13.3</v>
+      </c>
+      <c r="F7">
+        <v>18.4</v>
+      </c>
+      <c r="G7">
+        <v>27.6</v>
+      </c>
+      <c r="H7">
+        <v>23.3</v>
+      </c>
+      <c r="I7">
+        <v>6.4</v>
+      </c>
+      <c r="J7">
+        <v>0.8</v>
+      </c>
+      <c r="K7">
         <v>0.1</v>
       </c>
-      <c r="C7">
-        <v>1.4</v>
-      </c>
-      <c r="D7">
-        <v>5.3</v>
-      </c>
-      <c r="E7">
-        <v>16.2</v>
-      </c>
-      <c r="F7">
-        <v>26.1</v>
-      </c>
-      <c r="G7">
-        <v>33.1</v>
-      </c>
-      <c r="H7">
-        <v>10.8</v>
-      </c>
-      <c r="I7">
-        <v>4.4</v>
-      </c>
-      <c r="J7">
-        <v>1.9</v>
-      </c>
-      <c r="K7">
-        <v>0.7</v>
-      </c>
       <c r="L7">
-        <v>82.2</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1876,37 +1911,37 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="D8">
-        <v>0.1</v>
+        <v>4.2</v>
       </c>
       <c r="E8">
-        <v>1.1</v>
+        <v>8.5</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>12.9</v>
       </c>
       <c r="G8">
-        <v>10.3</v>
+        <v>21.6</v>
       </c>
       <c r="H8">
-        <v>28.7</v>
+        <v>35.4</v>
       </c>
       <c r="I8">
-        <v>22.7</v>
+        <v>13.6</v>
       </c>
       <c r="J8">
-        <v>22.6</v>
+        <v>1.9</v>
       </c>
       <c r="K8">
-        <v>11.5</v>
+        <v>0.2</v>
       </c>
       <c r="L8">
-        <v>14.5</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1920,31 +1955,31 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E9">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F9">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="G9">
-        <v>8.9</v>
+        <v>5.1</v>
       </c>
       <c r="H9">
-        <v>22.9</v>
+        <v>14.7</v>
       </c>
       <c r="I9">
-        <v>27.1</v>
+        <v>49</v>
       </c>
       <c r="J9">
-        <v>20.8</v>
+        <v>22.4</v>
       </c>
       <c r="K9">
-        <v>16.3</v>
+        <v>6.4</v>
       </c>
       <c r="L9">
-        <v>12.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1958,31 +1993,31 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="G10">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="H10">
-        <v>14.6</v>
+        <v>3.2</v>
       </c>
       <c r="I10">
-        <v>25.9</v>
+        <v>19.5</v>
       </c>
       <c r="J10">
-        <v>27.2</v>
+        <v>49</v>
       </c>
       <c r="K10">
-        <v>24.3</v>
+        <v>26.7</v>
       </c>
       <c r="L10">
-        <v>8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2002,25 +2037,25 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="H11">
-        <v>10.2</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="J11">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="K11">
-        <v>47</v>
+        <v>66.5</v>
       </c>
       <c r="L11">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2030,27 +2065,30 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>37</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -2067,90 +2105,105 @@
         <v>100</v>
       </c>
       <c r="F2">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G2">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>91.2</v>
+        <v>1.3</v>
       </c>
       <c r="C3">
-        <v>97.7</v>
+        <v>31.7</v>
       </c>
       <c r="D3">
-        <v>98.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>86.5</v>
       </c>
       <c r="F3">
-        <v>99.90000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>98.2</v>
+      </c>
+      <c r="G3">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B4">
-        <v>98</v>
+        <v>98.2</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
       <c r="E4">
         <v>99.40000000000001</v>
       </c>
       <c r="F4">
-        <v>99.59999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="G4">
+        <v>94.19999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5">
+        <v>91.3</v>
+      </c>
+      <c r="C5">
+        <v>97.39999999999999</v>
+      </c>
+      <c r="D5">
+        <v>99.2</v>
+      </c>
+      <c r="E5">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="F5">
+        <v>93.30000000000001</v>
+      </c>
+      <c r="G5">
+        <v>93.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="C5">
-        <v>38.9</v>
-      </c>
-      <c r="D5">
-        <v>95.39999999999999</v>
-      </c>
-      <c r="E5">
-        <v>94.09999999999999</v>
-      </c>
-      <c r="F5">
-        <v>94.59999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B6">
-        <v>0.8999999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="C6">
-        <v>27.9</v>
+        <v>37.4</v>
       </c>
       <c r="D6">
-        <v>87.40000000000001</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="E6">
-        <v>85.2</v>
+        <v>94.19999999999999</v>
       </c>
       <c r="F6">
-        <v>89.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>89.2</v>
+      </c>
+      <c r="G6">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -2158,59 +2211,68 @@
         <v>99.5</v>
       </c>
       <c r="C7">
-        <v>92.80000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="D7">
-        <v>30.1</v>
+        <v>33.4</v>
       </c>
       <c r="E7">
-        <v>81.39999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="F7">
-        <v>80.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="G7">
+        <v>66.40000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C8">
-        <v>36.8</v>
+        <v>33.5</v>
       </c>
       <c r="D8">
-        <v>41.5</v>
+        <v>35.3</v>
       </c>
       <c r="E8">
-        <v>15</v>
+        <v>15.4</v>
       </c>
       <c r="F8">
-        <v>13.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>47.4</v>
+      </c>
+      <c r="G8">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B9">
-        <v>98.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="C9">
-        <v>70.19999999999999</v>
+        <v>70.39999999999999</v>
       </c>
       <c r="D9">
-        <v>41.3</v>
+        <v>40.7</v>
       </c>
       <c r="E9">
-        <v>13.6</v>
+        <v>12.7</v>
       </c>
       <c r="F9">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>10.4</v>
+      </c>
+      <c r="G9">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -2221,33 +2283,39 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E10">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="F10">
-        <v>7.399999999999999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>1.3</v>
+      </c>
+      <c r="G10">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B11">
-        <v>35.09999999999999</v>
+        <v>34.7</v>
       </c>
       <c r="C11">
-        <v>35.7</v>
+        <v>36.1</v>
       </c>
       <c r="D11">
-        <v>5.600000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="E11">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="F11">
-        <v>2.7</v>
+        <v>0.5</v>
+      </c>
+      <c r="G11">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -2262,28 +2330,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2294,25 +2362,25 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2">
-        <v>91.93000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>110.91</v>
+        <v>113.96</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2320,28 +2388,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3">
-        <v>101.73</v>
+        <v>95.38</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>113.22</v>
+        <v>113.3</v>
       </c>
       <c r="G3">
-        <v>0.575</v>
+        <v>0.533</v>
       </c>
       <c r="H3">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2349,28 +2417,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4">
-        <v>123.18</v>
+        <v>98.16</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>109.1</v>
+        <v>112.99</v>
       </c>
       <c r="G4">
-        <v>0.475</v>
+        <v>0.511</v>
       </c>
       <c r="H4">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2378,28 +2446,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5">
+        <v>115.3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>111.09</v>
+      </c>
+      <c r="G5">
+        <v>0.489</v>
+      </c>
+      <c r="H5">
+        <v>0.4</v>
+      </c>
+      <c r="I5">
         <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5">
-        <v>113.43</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5">
-        <v>111.27</v>
-      </c>
-      <c r="G5">
-        <v>0.525</v>
-      </c>
-      <c r="H5">
-        <v>0.2</v>
-      </c>
-      <c r="I5">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2407,28 +2475,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>96.2</v>
+        <v>119.04</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>112.26</v>
+        <v>110.67</v>
       </c>
       <c r="G6">
-        <v>0.525</v>
+        <v>0.489</v>
       </c>
       <c r="H6">
         <v>0.1</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2436,28 +2504,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7">
-        <v>115.36</v>
+        <v>109.27</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>108.43</v>
+        <v>111.76</v>
       </c>
       <c r="G7">
-        <v>0.475</v>
+        <v>0.489</v>
       </c>
       <c r="H7">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2465,28 +2533,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>110.76</v>
+        <v>111.58</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
       </c>
       <c r="F8">
-        <v>111.59</v>
+        <v>111.5</v>
       </c>
       <c r="G8">
-        <v>0.525</v>
+        <v>0.511</v>
       </c>
       <c r="H8">
-        <v>-0.4</v>
+        <v>-0.6</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2497,25 +2565,25 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>122.72</v>
+        <v>119.47</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>109.42</v>
+        <v>110.63</v>
       </c>
       <c r="G9">
-        <v>0.475</v>
+        <v>0.489</v>
       </c>
       <c r="H9">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2523,28 +2591,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>130.53</v>
+        <v>128.27</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>107.46</v>
+        <v>109.65</v>
       </c>
       <c r="G10">
-        <v>0.425</v>
+        <v>0.489</v>
       </c>
       <c r="H10">
-        <v>-1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2552,28 +2620,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11">
-        <v>97.59</v>
+        <v>129.13</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
       </c>
       <c r="F11">
-        <v>109.78</v>
+        <v>109.55</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="H11">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2588,31 +2656,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2620,16 +2688,16 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D2">
-        <v>130.535</v>
+        <v>129.132</v>
       </c>
       <c r="E2">
-        <v>522.14</v>
+        <v>645.66</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2638,39 +2706,39 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D3">
-        <v>123.18</v>
+        <v>128.272</v>
       </c>
       <c r="E3">
-        <v>492.72</v>
+        <v>641.36</v>
       </c>
       <c r="F3">
-        <v>99.90000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2678,86 +2746,86 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D4">
-        <v>122.715</v>
+        <v>119.472</v>
       </c>
       <c r="E4">
-        <v>490.86</v>
+        <v>597.36</v>
       </c>
       <c r="F4">
-        <v>99.8</v>
+        <v>94.3</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D5">
-        <v>115.365</v>
+        <v>119.044</v>
       </c>
       <c r="E5">
-        <v>461.46</v>
+        <v>595.22</v>
       </c>
       <c r="F5">
-        <v>94.39999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D6">
-        <v>113.425</v>
+        <v>115.3</v>
       </c>
       <c r="E6">
-        <v>453.7</v>
+        <v>576.5</v>
       </c>
       <c r="F6">
-        <v>85.8</v>
+        <v>86.3</v>
       </c>
       <c r="G6">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2765,28 +2833,28 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D7">
-        <v>110.76</v>
+        <v>109.268</v>
       </c>
       <c r="E7">
-        <v>443.04</v>
+        <v>546.3399999999999</v>
       </c>
       <c r="F7">
-        <v>82.19999999999999</v>
+        <v>69.39999999999999</v>
       </c>
       <c r="G7">
-        <v>0.7000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="H7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2794,28 +2862,28 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D8">
-        <v>101.735</v>
+        <v>111.58</v>
       </c>
       <c r="E8">
-        <v>406.9399999999999</v>
+        <v>557.9</v>
       </c>
       <c r="F8">
-        <v>14.5</v>
+        <v>48.9</v>
       </c>
       <c r="G8">
-        <v>11.5</v>
+        <v>0.2</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2823,28 +2891,28 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D9">
-        <v>97.595</v>
+        <v>98.15599999999999</v>
       </c>
       <c r="E9">
-        <v>390.38</v>
+        <v>490.78</v>
       </c>
       <c r="F9">
-        <v>12.9</v>
+        <v>7.5</v>
       </c>
       <c r="G9">
-        <v>16.3</v>
+        <v>6.4</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2852,28 +2920,28 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D10">
-        <v>96.2</v>
+        <v>95.384</v>
       </c>
       <c r="E10">
-        <v>384.8</v>
+        <v>476.92</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="G10">
-        <v>24.3</v>
+        <v>26.7</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2881,28 +2949,28 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C11">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D11">
-        <v>91.93499999999999</v>
+        <v>89.496</v>
       </c>
       <c r="E11">
-        <v>367.74</v>
+        <v>447.48</v>
       </c>
       <c r="F11">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="G11">
-        <v>47</v>
+        <v>66.5</v>
       </c>
       <c r="H11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2917,19 +2985,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2940,16 +3008,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2957,19 +3025,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2977,19 +3045,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2997,19 +3065,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3017,19 +3085,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3037,19 +3105,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3063,13 +3131,13 @@
         <v>49</v>
       </c>
       <c r="D8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3077,19 +3145,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D9">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3100,16 +3168,16 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D10">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3120,16 +3188,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11">
-        <v>-10</v>
+        <v>-19</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3139,27 +3207,30 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>99</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -3175,111 +3246,129 @@
       <c r="E2">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>-4</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
         <v>4</v>
       </c>
-      <c r="F4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5">
+      <c r="G6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
-        <v>-6</v>
-      </c>
       <c r="C7">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>-1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -3295,31 +3384,37 @@
       <c r="E8">
         <v>-2</v>
       </c>
-      <c r="F8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="F8">
+        <v>-4</v>
+      </c>
+      <c r="G8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9">
-        <v>-4</v>
-      </c>
-      <c r="F9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>-6</v>
+      </c>
+      <c r="G9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -3335,11 +3430,14 @@
       <c r="E10">
         <v>-4</v>
       </c>
-      <c r="F10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10">
+        <v>-7</v>
+      </c>
+      <c r="G10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -3355,8 +3453,11 @@
       <c r="E11">
         <v>-10</v>
       </c>
-      <c r="F11" t="s">
-        <v>92</v>
+      <c r="F11">
+        <v>-19</v>
+      </c>
+      <c r="G11" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Operators Football League 2026.xlsx
+++ b/data/leagues/Operators Football League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="110">
   <si>
     <t>Junya Ettlinger's First Team</t>
   </si>
@@ -55,22 +55,25 @@
     <t>Hall Pass</t>
   </si>
   <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>4-1-0</t>
-  </si>
-  <si>
-    <t>1-4-0</t>
-  </si>
-  <si>
-    <t>5-0-0</t>
-  </si>
-  <si>
-    <t>0-5-0</t>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>5-1-0</t>
+  </si>
+  <si>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>1-5-0</t>
+  </si>
+  <si>
+    <t>6-0-0</t>
+  </si>
+  <si>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>0-6-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -142,6 +145,9 @@
     <t>Week_6</t>
   </si>
   <si>
+    <t>Week_7</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -163,36 +169,36 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Carly Foster</t>
+  </si>
+  <si>
     <t>Julie Williston</t>
   </si>
   <si>
+    <t>Morgan Herber</t>
+  </si>
+  <si>
+    <t>Rachel Hall</t>
+  </si>
+  <si>
+    <t>Jessica McNally</t>
+  </si>
+  <si>
     <t>Casey Reid</t>
   </si>
   <si>
     <t>Lauren Ettlinger</t>
   </si>
   <si>
-    <t>Carly Foster</t>
-  </si>
-  <si>
-    <t>Morgan Herber</t>
-  </si>
-  <si>
     <t>Haley Toadvine</t>
   </si>
   <si>
-    <t>Jessica McNally</t>
+    <t>Katie  Kush</t>
   </si>
   <si>
     <t>Ava Patterson</t>
   </si>
   <si>
-    <t>Rachel Hall</t>
-  </si>
-  <si>
-    <t>Katie  Kush</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -217,43 +223,43 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>10.8-3.1-0.1</t>
-  </si>
-  <si>
-    <t>9.2-4.8-0.1</t>
-  </si>
-  <si>
-    <t>8.4-5.5-0.1</t>
-  </si>
-  <si>
-    <t>7.9-6.0-0.1</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>11.1-2.8-0.1</t>
+  </si>
+  <si>
+    <t>8.9-5.0-0.1</t>
+  </si>
+  <si>
+    <t>8.1-5.8-0.1</t>
+  </si>
+  <si>
+    <t>7.4-6.5-0.1</t>
   </si>
   <si>
     <t>7.2-6.7-0.1</t>
   </si>
   <si>
-    <t>6.5-7.4-0.1</t>
-  </si>
-  <si>
-    <t>4.8-9.1-0.1</t>
-  </si>
-  <si>
-    <t>3.5-10.4-0.1</t>
-  </si>
-  <si>
-    <t>2.8-11.1-0.1</t>
+    <t>7.1-6.8-0.1</t>
+  </si>
+  <si>
+    <t>6.3-7.6-0.1</t>
+  </si>
+  <si>
+    <t>3.4-10.5-0.1</t>
+  </si>
+  <si>
+    <t>2.7-11.3-0.1</t>
   </si>
   <si>
     <t>11-3</t>
@@ -268,12 +274,15 @@
     <t>7-7</t>
   </si>
   <si>
-    <t>5-9</t>
+    <t>6-8</t>
   </si>
   <si>
     <t>3-11</t>
   </si>
   <si>
+    <t>2-12</t>
+  </si>
+  <si>
     <t>Owners</t>
   </si>
   <si>
@@ -283,33 +292,30 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>↑6</t>
   </si>
   <si>
-    <t>↑4</t>
-  </si>
-  <si>
-    <t>↑7</t>
-  </si>
-  <si>
-    <t>↑9</t>
-  </si>
-  <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>↓3</t>
-  </si>
-  <si>
     <t>↓2</t>
   </si>
   <si>
-    <t>↓7</t>
+    <t>↓6</t>
+  </si>
+  <si>
+    <t>↑8</t>
+  </si>
+  <si>
+    <t>↑3</t>
   </si>
   <si>
     <t>↓9</t>
   </si>
   <si>
+    <t>↓5</t>
+  </si>
+  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -323,6 +329,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -744,10 +753,10 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -756,13 +765,13 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
         <v>12</v>
@@ -776,34 +785,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" t="s">
         <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -811,34 +820,34 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -846,34 +855,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
         <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -884,13 +893,13 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
@@ -899,16 +908,16 @@
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
         <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -916,34 +925,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
         <v>11</v>
       </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" t="s">
-        <v>12</v>
-      </c>
       <c r="I7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -957,25 +966,25 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
       </c>
       <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
         <v>12</v>
       </c>
-      <c r="G8" t="s">
-        <v>10</v>
-      </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I8" t="s">
         <v>12</v>
       </c>
       <c r="J8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K8" t="s">
         <v>14</v>
@@ -986,34 +995,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I9" t="s">
         <v>13</v>
       </c>
       <c r="J9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1021,7 +1030,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
         <v>10</v>
@@ -1036,19 +1045,19 @@
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
         <v>12</v>
       </c>
       <c r="I10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J10" t="s">
         <v>10</v>
       </c>
       <c r="K10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1056,7 +1065,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
@@ -1065,25 +1074,25 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
         <v>12</v>
       </c>
       <c r="H11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" t="s">
         <v>12</v>
-      </c>
-      <c r="I11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" t="s">
-        <v>10</v>
-      </c>
-      <c r="K11" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1093,30 +1102,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1124,25 +1133,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1150,25 +1159,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1176,25 +1185,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>-4</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1202,25 +1211,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1231,22 +1240,22 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1254,24 +1263,50 @@
         <v>5</v>
       </c>
       <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
         <v>5</v>
       </c>
-      <c r="D7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="D8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1287,13 +1322,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1301,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1315,13 +1350,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1329,13 +1364,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1343,10 +1378,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1360,7 +1395,7 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -1371,10 +1406,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1385,13 +1420,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1402,10 +1437,10 @@
         <v>3</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1416,10 +1451,10 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1430,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1448,16 +1483,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1468,13 +1503,13 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="D2">
-        <v>0.09999999999999964</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1482,16 +1517,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D3">
-        <v>0.2999999999999998</v>
+        <v>-0.5</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1499,13 +1534,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>0.1000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1516,13 +1551,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="D5">
-        <v>0.1000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1536,10 +1571,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="D6">
-        <v>-0.2999999999999998</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1553,13 +1588,13 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="D7">
-        <v>-0.2999999999999998</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1567,16 +1602,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1587,13 +1622,13 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="D9">
-        <v>-0.6000000000000001</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1604,10 +1639,10 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="D10">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
@@ -1621,10 +1656,10 @@
         <v>4</v>
       </c>
       <c r="C11">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D11">
-        <v>-0.2</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -1642,40 +1677,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1683,22 +1718,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>68.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="C2">
-        <v>20.9</v>
+        <v>12.6</v>
       </c>
       <c r="D2">
-        <v>6.1</v>
+        <v>1.9</v>
       </c>
       <c r="E2">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="F2">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G2">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1721,151 +1756,151 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>18.7</v>
+        <v>9.9</v>
       </c>
       <c r="C3">
-        <v>32.1</v>
+        <v>38.5</v>
       </c>
       <c r="D3">
-        <v>22.3</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>12.8</v>
+        <v>13.7</v>
       </c>
       <c r="F3">
-        <v>7.9</v>
+        <v>6.3</v>
       </c>
       <c r="G3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H3">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="I3">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>98.09999999999999</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="C4">
-        <v>16.2</v>
+        <v>17.8</v>
       </c>
       <c r="D4">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="E4">
-        <v>21.4</v>
+        <v>18.3</v>
       </c>
       <c r="F4">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="G4">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="H4">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I4">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>94.3</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="C5">
-        <v>17.3</v>
+        <v>10.7</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>14.9</v>
       </c>
       <c r="E5">
-        <v>21.5</v>
+        <v>17.7</v>
       </c>
       <c r="F5">
-        <v>18.5</v>
+        <v>19.1</v>
       </c>
       <c r="G5">
+        <v>14.9</v>
+      </c>
+      <c r="H5">
+        <v>11</v>
+      </c>
+      <c r="I5">
         <v>10.3</v>
       </c>
-      <c r="H5">
-        <v>5.3</v>
-      </c>
-      <c r="I5">
-        <v>0.7</v>
-      </c>
       <c r="J5">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>93.8</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B6">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="C6">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>13.9</v>
       </c>
       <c r="E6">
-        <v>18.6</v>
+        <v>15.3</v>
       </c>
       <c r="F6">
-        <v>20.5</v>
+        <v>16.8</v>
       </c>
       <c r="G6">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I6">
-        <v>2.2</v>
+        <v>10.1</v>
       </c>
       <c r="J6">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="K6">
         <v>0.1</v>
       </c>
       <c r="L6">
-        <v>86.3</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1873,75 +1908,75 @@
         <v>2</v>
       </c>
       <c r="B7">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="D7">
-        <v>6.9</v>
+        <v>11.5</v>
       </c>
       <c r="E7">
-        <v>13.3</v>
+        <v>15.4</v>
       </c>
       <c r="F7">
-        <v>18.4</v>
+        <v>16.6</v>
       </c>
       <c r="G7">
-        <v>27.6</v>
+        <v>18.8</v>
       </c>
       <c r="H7">
-        <v>23.3</v>
+        <v>15.9</v>
       </c>
       <c r="I7">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="J7">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="K7">
         <v>0.1</v>
       </c>
       <c r="L7">
-        <v>69.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B8">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C8">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="D8">
-        <v>4.2</v>
+        <v>10.3</v>
       </c>
       <c r="E8">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="F8">
-        <v>12.9</v>
+        <v>16.6</v>
       </c>
       <c r="G8">
-        <v>21.6</v>
+        <v>17.1</v>
       </c>
       <c r="H8">
-        <v>35.4</v>
+        <v>19.9</v>
       </c>
       <c r="I8">
-        <v>13.6</v>
+        <v>15.7</v>
       </c>
       <c r="J8">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K8">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="L8">
-        <v>48.9</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1949,37 +1984,37 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D9">
-        <v>0.2</v>
+        <v>2.6</v>
       </c>
       <c r="E9">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="F9">
-        <v>1.5</v>
+        <v>8.4</v>
       </c>
       <c r="G9">
+        <v>14.3</v>
+      </c>
+      <c r="H9">
+        <v>24.6</v>
+      </c>
+      <c r="I9">
+        <v>37.8</v>
+      </c>
+      <c r="J9">
         <v>5.1</v>
       </c>
-      <c r="H9">
-        <v>14.7</v>
-      </c>
-      <c r="I9">
-        <v>49</v>
-      </c>
-      <c r="J9">
-        <v>22.4</v>
-      </c>
       <c r="K9">
-        <v>6.4</v>
+        <v>0.1</v>
       </c>
       <c r="L9">
-        <v>7.5</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1999,25 +2034,25 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G10">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="H10">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="I10">
-        <v>19.5</v>
+        <v>6.3</v>
       </c>
       <c r="J10">
-        <v>49</v>
+        <v>66.5</v>
       </c>
       <c r="K10">
-        <v>26.7</v>
+        <v>24.8</v>
       </c>
       <c r="L10">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2043,16 +2078,16 @@
         <v>0.1</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I11">
-        <v>7.2</v>
+        <v>1.9</v>
       </c>
       <c r="J11">
-        <v>25.2</v>
+        <v>23.2</v>
       </c>
       <c r="K11">
-        <v>66.5</v>
+        <v>74.5</v>
       </c>
       <c r="L11">
         <v>0.1</v>
@@ -2065,35 +2100,38 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>39</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -2110,169 +2148,193 @@
       <c r="G2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>1.3</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="C3">
         <v>31.7</v>
       </c>
       <c r="D3">
+        <v>85.7</v>
+      </c>
+      <c r="E3">
+        <v>83.7</v>
+      </c>
+      <c r="F3">
+        <v>98</v>
+      </c>
+      <c r="G3">
+        <v>96.89999999999999</v>
+      </c>
+      <c r="H3">
+        <v>96.39999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>80.30000000000001</v>
+      </c>
+      <c r="C4">
+        <v>37.7</v>
+      </c>
+      <c r="D4">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="E4">
+        <v>93.89999999999999</v>
+      </c>
+      <c r="F4">
+        <v>88.7</v>
+      </c>
+      <c r="G4">
         <v>89.5</v>
       </c>
-      <c r="E3">
-        <v>86.5</v>
-      </c>
-      <c r="F3">
-        <v>98.2</v>
-      </c>
-      <c r="G3">
-        <v>96.8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+      <c r="H4">
+        <v>88.59999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>36.4</v>
+      </c>
+      <c r="D5">
+        <v>39.7</v>
+      </c>
+      <c r="E5">
+        <v>15.8</v>
+      </c>
+      <c r="F5">
+        <v>45.6</v>
+      </c>
+      <c r="G5">
+        <v>81.3</v>
+      </c>
+      <c r="H5">
+        <v>76.09999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>98.2</v>
-      </c>
-      <c r="C4">
+      <c r="B6">
+        <v>98.3</v>
+      </c>
+      <c r="C6">
         <v>100</v>
       </c>
-      <c r="D4">
-        <v>99.5</v>
-      </c>
-      <c r="E4">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="F4">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="G4">
-        <v>94.19999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>91.3</v>
-      </c>
-      <c r="C5">
-        <v>97.39999999999999</v>
-      </c>
-      <c r="D5">
-        <v>99.2</v>
-      </c>
-      <c r="E5">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="F5">
-        <v>93.30000000000001</v>
-      </c>
-      <c r="G5">
-        <v>93.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>76.8</v>
-      </c>
-      <c r="C6">
-        <v>37.4</v>
-      </c>
       <c r="D6">
-        <v>94.19999999999999</v>
+        <v>100</v>
       </c>
       <c r="E6">
-        <v>94.19999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="F6">
-        <v>89.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="G6">
-        <v>85.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>65.2</v>
+      </c>
+      <c r="H6">
+        <v>73.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B7">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="C7">
-        <v>93.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D7">
-        <v>33.4</v>
+        <v>30.6</v>
       </c>
       <c r="E7">
-        <v>78.2</v>
+        <v>77.2</v>
       </c>
       <c r="F7">
-        <v>67.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="G7">
-        <v>66.40000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>70.19999999999999</v>
+      </c>
+      <c r="H7">
+        <v>67.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B8">
-        <v>0.1</v>
+        <v>89.8</v>
       </c>
       <c r="C8">
-        <v>33.5</v>
+        <v>98.8</v>
       </c>
       <c r="D8">
-        <v>35.3</v>
+        <v>99.2</v>
       </c>
       <c r="E8">
-        <v>15.4</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F8">
-        <v>47.4</v>
+        <v>94.89999999999999</v>
       </c>
       <c r="G8">
-        <v>54.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>62.5</v>
+      </c>
+      <c r="H8">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B9">
-        <v>98.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="C9">
-        <v>70.39999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="D9">
-        <v>40.7</v>
+        <v>42.6</v>
       </c>
       <c r="E9">
-        <v>12.7</v>
+        <v>15.9</v>
       </c>
       <c r="F9">
-        <v>10.4</v>
+        <v>12.6</v>
       </c>
       <c r="G9">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>33.6</v>
+      </c>
+      <c r="H9">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -2283,38 +2345,44 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="E10">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="F10">
         <v>1.3</v>
       </c>
       <c r="G10">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>0.6</v>
+      </c>
+      <c r="H10">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B11">
-        <v>34.7</v>
+        <v>33.5</v>
       </c>
       <c r="C11">
-        <v>36.1</v>
+        <v>30.8</v>
       </c>
       <c r="D11">
-        <v>7.9</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="E11">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="F11">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G11">
+        <v>0.2</v>
+      </c>
+      <c r="H11">
         <v>0.3</v>
       </c>
     </row>
@@ -2330,28 +2398,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2359,28 +2427,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>89.5</v>
+        <v>113.17</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>113.96</v>
+        <v>110.76</v>
       </c>
       <c r="G2">
-        <v>0.533</v>
+        <v>0.521</v>
       </c>
       <c r="H2">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2388,28 +2456,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>95.38</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
       </c>
       <c r="F3">
-        <v>113.3</v>
+        <v>110.76</v>
       </c>
       <c r="G3">
-        <v>0.533</v>
+        <v>0.521</v>
       </c>
       <c r="H3">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2417,28 +2485,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>98.16</v>
+        <v>108.8</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>112.99</v>
+        <v>106.89</v>
       </c>
       <c r="G4">
-        <v>0.511</v>
+        <v>0.479</v>
       </c>
       <c r="H4">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2446,28 +2514,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <v>115.3</v>
+        <v>119.81</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>111.09</v>
+        <v>106.89</v>
       </c>
       <c r="G5">
-        <v>0.489</v>
+        <v>0.479</v>
       </c>
       <c r="H5">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2475,28 +2543,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>119.04</v>
+        <v>114.17</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6">
-        <v>110.67</v>
+        <v>109.59</v>
       </c>
       <c r="G6">
-        <v>0.489</v>
+        <v>0.542</v>
       </c>
       <c r="H6">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2504,28 +2572,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>109.27</v>
+        <v>92.91</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F7">
-        <v>111.76</v>
+        <v>109.59</v>
       </c>
       <c r="G7">
-        <v>0.489</v>
+        <v>0.542</v>
       </c>
       <c r="H7">
-        <v>-0.4</v>
+        <v>-1</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2533,28 +2601,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D8">
-        <v>111.58</v>
+        <v>102.1</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>111.5</v>
+        <v>108.84</v>
       </c>
       <c r="G8">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="H8">
-        <v>-0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2562,28 +2630,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9">
+        <v>110.93</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>108.84</v>
+      </c>
+      <c r="G9">
+        <v>0.5</v>
+      </c>
+      <c r="H9">
+        <v>-1.6</v>
+      </c>
+      <c r="I9">
         <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9">
-        <v>119.47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9">
-        <v>110.63</v>
-      </c>
-      <c r="G9">
-        <v>0.489</v>
-      </c>
-      <c r="H9">
-        <v>-0.9</v>
-      </c>
-      <c r="I9">
-        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2591,28 +2659,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10">
-        <v>128.27</v>
+        <v>127.46</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10">
-        <v>109.65</v>
+        <v>105.8</v>
       </c>
       <c r="G10">
-        <v>0.489</v>
+        <v>0.458</v>
       </c>
       <c r="H10">
-        <v>-0.9</v>
+        <v>-2.4</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2620,28 +2688,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>129.13</v>
+        <v>109.93</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>109.55</v>
+        <v>105.8</v>
       </c>
       <c r="G11">
-        <v>0.467</v>
+        <v>0.458</v>
       </c>
       <c r="H11">
-        <v>-1.3</v>
+        <v>-2.4</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2656,31 +2724,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2688,16 +2756,16 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D2">
-        <v>129.132</v>
+        <v>127.4566666666667</v>
       </c>
       <c r="E2">
-        <v>645.66</v>
+        <v>764.74</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2706,10 +2774,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2717,115 +2785,115 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>128.272</v>
+        <v>119.81</v>
       </c>
       <c r="E3">
-        <v>641.36</v>
+        <v>718.86</v>
       </c>
       <c r="F3">
-        <v>98.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>119.472</v>
+        <v>113.1733333333333</v>
       </c>
       <c r="E4">
-        <v>597.36</v>
+        <v>679.04</v>
       </c>
       <c r="F4">
-        <v>94.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>119.044</v>
+        <v>114.1666666666667</v>
       </c>
       <c r="E5">
-        <v>595.22</v>
+        <v>685</v>
       </c>
       <c r="F5">
-        <v>93.8</v>
+        <v>78.2</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C6">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>115.3</v>
+        <v>109.9266666666667</v>
       </c>
       <c r="E6">
-        <v>576.5</v>
+        <v>659.5600000000001</v>
       </c>
       <c r="F6">
-        <v>86.3</v>
+        <v>73.5</v>
       </c>
       <c r="G6">
         <v>0.1</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2833,57 +2901,57 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C7">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>109.268</v>
+        <v>110.93</v>
       </c>
       <c r="E7">
-        <v>546.3399999999999</v>
+        <v>665.5799999999999</v>
       </c>
       <c r="F7">
-        <v>69.39999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G7">
         <v>0.1</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8">
+        <v>0.5</v>
+      </c>
+      <c r="D8">
+        <v>108.8</v>
+      </c>
+      <c r="E8">
+        <v>652.8000000000001</v>
+      </c>
+      <c r="F8">
+        <v>62.3</v>
+      </c>
+      <c r="G8">
         <v>0.4</v>
       </c>
-      <c r="D8">
-        <v>111.58</v>
-      </c>
-      <c r="E8">
-        <v>557.9</v>
-      </c>
-      <c r="F8">
-        <v>48.9</v>
-      </c>
-      <c r="G8">
-        <v>0.2</v>
-      </c>
       <c r="H8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2891,28 +2959,28 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>98.15599999999999</v>
+        <v>102.1033333333333</v>
       </c>
       <c r="E9">
-        <v>490.78</v>
+        <v>612.62</v>
       </c>
       <c r="F9">
-        <v>7.5</v>
+        <v>32.4</v>
       </c>
       <c r="G9">
-        <v>6.4</v>
+        <v>0.1</v>
       </c>
       <c r="H9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2920,28 +2988,28 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C10">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D10">
-        <v>95.384</v>
+        <v>92.90666666666668</v>
       </c>
       <c r="E10">
-        <v>476.92</v>
+        <v>557.4400000000001</v>
       </c>
       <c r="F10">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="G10">
-        <v>26.7</v>
+        <v>24.8</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2949,28 +3017,28 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C11">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D11">
-        <v>89.496</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="E11">
-        <v>447.48</v>
+        <v>506.9399999999999</v>
       </c>
       <c r="F11">
         <v>0.1</v>
       </c>
       <c r="G11">
-        <v>66.5</v>
+        <v>74.5</v>
       </c>
       <c r="H11" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2985,19 +3053,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3008,16 +3076,16 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3025,19 +3093,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3045,19 +3113,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3065,19 +3133,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3085,19 +3153,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
         <v>51</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3105,19 +3173,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3125,19 +3193,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D8">
         <v>-4</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3145,7 +3213,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
         <v>48</v>
@@ -3154,10 +3222,10 @@
         <v>-6</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3165,19 +3233,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D10">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3188,16 +3256,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>-19</v>
+        <v>-24</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3207,30 +3275,33 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>102</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -3249,195 +3320,222 @@
       <c r="F2">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="G2">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>-4</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3">
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C3">
+      <c r="C5">
         <v>5</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>4</v>
       </c>
-      <c r="F3">
+      <c r="F5">
         <v>8</v>
       </c>
-      <c r="G3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="H5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
+      <c r="B6">
         <v>-6</v>
       </c>
-      <c r="C4">
+      <c r="C6">
         <v>-4</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="G4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
+      <c r="G6">
         <v>2</v>
       </c>
-      <c r="E5">
+      <c r="H6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>-6</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>-2</v>
+      </c>
+      <c r="C8">
         <v>-4</v>
       </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
+      <c r="D8">
+        <v>-5</v>
+      </c>
+      <c r="E8">
+        <v>-4</v>
+      </c>
+      <c r="F8">
+        <v>-7</v>
+      </c>
+      <c r="G8">
+        <v>-4</v>
+      </c>
+      <c r="H8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>-2</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>-2</v>
+      </c>
+      <c r="F9">
+        <v>-4</v>
+      </c>
+      <c r="G9">
+        <v>-6</v>
+      </c>
+      <c r="H9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>2</v>
       </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
+      <c r="F10">
         <v>-1</v>
       </c>
-      <c r="G7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>-2</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>-2</v>
-      </c>
-      <c r="F8">
-        <v>-4</v>
-      </c>
-      <c r="G8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>-6</v>
-      </c>
-      <c r="G9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>-2</v>
-      </c>
-      <c r="C10">
-        <v>-4</v>
-      </c>
-      <c r="D10">
-        <v>-5</v>
-      </c>
-      <c r="E10">
-        <v>-4</v>
-      </c>
-      <c r="F10">
-        <v>-7</v>
-      </c>
-      <c r="G10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="G10">
+        <v>-10</v>
+      </c>
+      <c r="H10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -3456,8 +3554,11 @@
       <c r="F11">
         <v>-19</v>
       </c>
-      <c r="G11" t="s">
-        <v>94</v>
+      <c r="G11">
+        <v>-24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Operators Football League 2026.xlsx
+++ b/data/leagues/Operators Football League 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="114">
   <si>
     <t>Junya Ettlinger's First Team</t>
   </si>
@@ -55,25 +55,28 @@
     <t>Hall Pass</t>
   </si>
   <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>5-1-0</t>
-  </si>
-  <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>1-5-0</t>
-  </si>
-  <si>
-    <t>6-0-0</t>
-  </si>
-  <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>0-6-0</t>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>1-6-0</t>
+  </si>
+  <si>
+    <t>7-0-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>0-7-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -148,6 +151,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -169,33 +175,33 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Julie Williston</t>
+  </si>
+  <si>
     <t>Carly Foster</t>
   </si>
   <si>
-    <t>Julie Williston</t>
+    <t>Casey Reid</t>
+  </si>
+  <si>
+    <t>Rachel Hall</t>
+  </si>
+  <si>
+    <t>Haley Toadvine</t>
+  </si>
+  <si>
+    <t>Jessica McNally</t>
+  </si>
+  <si>
+    <t>Katie  Kush</t>
   </si>
   <si>
     <t>Morgan Herber</t>
   </si>
   <si>
-    <t>Rachel Hall</t>
-  </si>
-  <si>
-    <t>Jessica McNally</t>
-  </si>
-  <si>
-    <t>Casey Reid</t>
-  </si>
-  <si>
     <t>Lauren Ettlinger</t>
   </si>
   <si>
-    <t>Haley Toadvine</t>
-  </si>
-  <si>
-    <t>Katie  Kush</t>
-  </si>
-  <si>
     <t>Ava Patterson</t>
   </si>
   <si>
@@ -223,46 +229,55 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>11.1-2.8-0.1</t>
-  </si>
-  <si>
-    <t>8.9-5.0-0.1</t>
-  </si>
-  <si>
-    <t>8.1-5.8-0.1</t>
-  </si>
-  <si>
-    <t>7.4-6.5-0.1</t>
-  </si>
-  <si>
-    <t>7.2-6.7-0.1</t>
-  </si>
-  <si>
-    <t>7.1-6.8-0.1</t>
-  </si>
-  <si>
-    <t>6.3-7.6-0.1</t>
-  </si>
-  <si>
-    <t>3.4-10.5-0.1</t>
-  </si>
-  <si>
-    <t>2.7-11.3-0.1</t>
-  </si>
-  <si>
-    <t>11-3</t>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>11.6-2.3-0.1</t>
+  </si>
+  <si>
+    <t>9.4-4.6-0.1</t>
+  </si>
+  <si>
+    <t>8.6-5.3-0.1</t>
+  </si>
+  <si>
+    <t>7.8-6.1-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.3-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>6.6-7.3-0.1</t>
+  </si>
+  <si>
+    <t>6.0-8.0-0.1</t>
+  </si>
+  <si>
+    <t>4.0-9.9-0.1</t>
+  </si>
+  <si>
+    <t>2.3-11.7-0.1</t>
+  </si>
+  <si>
+    <t>12-2</t>
   </si>
   <si>
     <t>9-5</t>
@@ -277,7 +292,7 @@
     <t>6-8</t>
   </si>
   <si>
-    <t>3-11</t>
+    <t>4-10</t>
   </si>
   <si>
     <t>2-12</t>
@@ -292,28 +307,22 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑6</t>
+    <t>↑4</t>
+  </si>
+  <si>
+    <t>↓1</t>
   </si>
   <si>
     <t>↓2</t>
   </si>
   <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↑8</t>
-  </si>
-  <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↓9</t>
-  </si>
-  <si>
-    <t>↓5</t>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↓4</t>
+  </si>
+  <si>
+    <t>↑1</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -332,6 +341,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -765,13 +777,13 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H2" t="s">
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
         <v>12</v>
@@ -800,13 +812,13 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" t="s">
         <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
       </c>
       <c r="J3" t="s">
         <v>12</v>
@@ -835,19 +847,19 @@
         <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J4" t="s">
         <v>12</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -861,28 +873,28 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
         <v>12</v>
       </c>
-      <c r="H5" t="s">
-        <v>10</v>
-      </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -905,7 +917,7 @@
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -931,28 +943,28 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -963,28 +975,28 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
       </c>
       <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
         <v>11</v>
       </c>
-      <c r="G8" t="s">
-        <v>12</v>
-      </c>
       <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" t="s">
         <v>11</v>
       </c>
-      <c r="I8" t="s">
-        <v>12</v>
-      </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K8" t="s">
         <v>14</v>
@@ -1001,28 +1013,28 @@
         <v>15</v>
       </c>
       <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
         <v>13</v>
       </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J9" t="s">
         <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1039,7 +1051,7 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -1068,31 +1080,31 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
         <v>11</v>
       </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" t="s">
         <v>12</v>
       </c>
-      <c r="H11" t="s">
+      <c r="J11" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" t="s">
         <v>11</v>
-      </c>
-      <c r="I11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" t="s">
-        <v>10</v>
-      </c>
-      <c r="K11" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1102,30 +1114,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1133,25 +1145,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
-        <v>1</v>
-      </c>
       <c r="E2">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1159,25 +1171,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1185,25 +1197,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1211,25 +1223,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>-4</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1237,77 +1249,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
-        <v>3</v>
-      </c>
       <c r="E6">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1322,13 +1282,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1336,13 +1296,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1350,13 +1310,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1367,7 +1327,7 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1378,13 +1338,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1392,13 +1352,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1406,13 +1366,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1423,10 +1383,10 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1434,13 +1394,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1448,10 +1408,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C10">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
@@ -1462,13 +1422,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1483,16 +1443,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1503,13 +1463,13 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="D2">
         <v>-0.2000000000000002</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1520,13 +1480,13 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="D3">
-        <v>-0.5</v>
+        <v>-0.5999999999999996</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1537,13 +1497,13 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1551,16 +1511,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="D5">
-        <v>0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1571,10 +1531,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D6">
-        <v>0.3999999999999999</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1585,16 +1545,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D7">
-        <v>-0.7000000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1605,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="D8">
-        <v>0.1000000000000001</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1622,10 +1582,10 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="D9">
-        <v>-0.7000000000000002</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -1639,13 +1599,13 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="D10">
-        <v>0.7</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1656,10 +1616,10 @@
         <v>4</v>
       </c>
       <c r="C11">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>-0.09999999999999998</v>
+        <v>0</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -1677,40 +1637,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1718,22 +1678,22 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>84.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="C2">
-        <v>12.6</v>
+        <v>8.1</v>
       </c>
       <c r="D2">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="E2">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F2">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1756,37 +1716,37 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
       <c r="C3">
-        <v>38.5</v>
+        <v>55.7</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>21.2</v>
       </c>
       <c r="E3">
-        <v>13.7</v>
+        <v>8.9</v>
       </c>
       <c r="F3">
-        <v>6.3</v>
+        <v>3.9</v>
       </c>
       <c r="G3">
-        <v>4.4</v>
+        <v>1.9</v>
       </c>
       <c r="H3">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="I3">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>96.8</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1794,37 +1754,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="C4">
-        <v>17.8</v>
+        <v>19.9</v>
       </c>
       <c r="D4">
-        <v>20.9</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>18.3</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>15.5</v>
+        <v>12.7</v>
       </c>
       <c r="G4">
-        <v>10.6</v>
+        <v>6.5</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="I4">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>86.40000000000001</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1832,151 +1792,151 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="C5">
-        <v>10.7</v>
+        <v>12.4</v>
       </c>
       <c r="D5">
-        <v>14.9</v>
+        <v>23.5</v>
       </c>
       <c r="E5">
-        <v>17.7</v>
+        <v>26.4</v>
       </c>
       <c r="F5">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="G5">
-        <v>14.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H5">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="I5">
-        <v>10.3</v>
+        <v>2.8</v>
       </c>
       <c r="J5">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>78.2</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B6">
+        <v>0.1</v>
+      </c>
+      <c r="C6">
+        <v>1.5</v>
+      </c>
+      <c r="D6">
+        <v>6.3</v>
+      </c>
+      <c r="E6">
+        <v>14.4</v>
+      </c>
+      <c r="F6">
+        <v>22.9</v>
+      </c>
+      <c r="G6">
+        <v>22.3</v>
+      </c>
+      <c r="H6">
+        <v>19</v>
+      </c>
+      <c r="I6">
+        <v>11.4</v>
+      </c>
+      <c r="J6">
+        <v>1.9</v>
+      </c>
+      <c r="K6">
         <v>0.2</v>
       </c>
-      <c r="C6">
-        <v>8.5</v>
-      </c>
-      <c r="D6">
-        <v>13.9</v>
-      </c>
-      <c r="E6">
-        <v>15.3</v>
-      </c>
-      <c r="F6">
-        <v>16.8</v>
-      </c>
-      <c r="G6">
-        <v>18.8</v>
-      </c>
-      <c r="H6">
-        <v>15</v>
-      </c>
-      <c r="I6">
-        <v>10.1</v>
-      </c>
-      <c r="J6">
-        <v>1.3</v>
-      </c>
-      <c r="K6">
-        <v>0.1</v>
-      </c>
       <c r="L6">
-        <v>73.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="D7">
-        <v>11.5</v>
+        <v>5.7</v>
       </c>
       <c r="E7">
-        <v>15.4</v>
+        <v>13.1</v>
       </c>
       <c r="F7">
-        <v>16.6</v>
+        <v>16.9</v>
       </c>
       <c r="G7">
-        <v>18.8</v>
+        <v>22.8</v>
       </c>
       <c r="H7">
-        <v>15.9</v>
+        <v>19.4</v>
       </c>
       <c r="I7">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="J7">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="K7">
         <v>0.1</v>
       </c>
       <c r="L7">
-        <v>69.09999999999999</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="D8">
-        <v>10.3</v>
+        <v>6.6</v>
       </c>
       <c r="E8">
-        <v>13.5</v>
+        <v>10.1</v>
       </c>
       <c r="F8">
-        <v>16.6</v>
+        <v>17.8</v>
       </c>
       <c r="G8">
-        <v>17.1</v>
+        <v>18.9</v>
       </c>
       <c r="H8">
-        <v>19.9</v>
+        <v>22.7</v>
       </c>
       <c r="I8">
-        <v>15.7</v>
+        <v>18</v>
       </c>
       <c r="J8">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="K8">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L8">
-        <v>62.3</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1984,37 +1944,37 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="E9">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="F9">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="G9">
-        <v>14.3</v>
+        <v>16.3</v>
       </c>
       <c r="H9">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="I9">
-        <v>37.8</v>
+        <v>35.6</v>
       </c>
       <c r="J9">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="K9">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="L9">
-        <v>32.4</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2031,28 +1991,28 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F10">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G10">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="H10">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="I10">
-        <v>6.3</v>
+        <v>14.3</v>
       </c>
       <c r="J10">
-        <v>66.5</v>
+        <v>71.8</v>
       </c>
       <c r="K10">
-        <v>24.8</v>
+        <v>7.7</v>
       </c>
       <c r="L10">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2078,16 +2038,16 @@
         <v>0.1</v>
       </c>
       <c r="H11">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I11">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J11">
-        <v>23.2</v>
+        <v>7.7</v>
       </c>
       <c r="K11">
-        <v>74.5</v>
+        <v>91.2</v>
       </c>
       <c r="L11">
         <v>0.1</v>
@@ -2100,33 +2060,36 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>41</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -2143,68 +2106,77 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
       <c r="H2">
-        <v>99.90000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>100</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0.8999999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="C3">
-        <v>31.7</v>
+        <v>33</v>
       </c>
       <c r="D3">
-        <v>85.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E3">
-        <v>83.7</v>
+        <v>83.89999999999999</v>
       </c>
       <c r="F3">
-        <v>98</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="G3">
-        <v>96.89999999999999</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="H3">
-        <v>96.39999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>98.8</v>
+      </c>
+      <c r="I3">
+        <v>99.09999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>80.30000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="C4">
-        <v>37.7</v>
+        <v>35.6</v>
       </c>
       <c r="D4">
-        <v>95.09999999999999</v>
+        <v>93.30000000000001</v>
       </c>
       <c r="E4">
-        <v>93.89999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="F4">
-        <v>88.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G4">
-        <v>89.5</v>
+        <v>91.2</v>
       </c>
       <c r="H4">
-        <v>88.59999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>95.8</v>
+      </c>
+      <c r="I4">
+        <v>96.59999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2212,129 +2184,144 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="D5">
-        <v>39.7</v>
+        <v>40.5</v>
       </c>
       <c r="E5">
-        <v>15.8</v>
+        <v>13.8</v>
       </c>
       <c r="F5">
-        <v>45.6</v>
+        <v>47.5</v>
       </c>
       <c r="G5">
-        <v>81.3</v>
+        <v>81.39999999999999</v>
       </c>
       <c r="H5">
-        <v>76.09999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>91.8</v>
+      </c>
+      <c r="I5">
+        <v>90.90000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>99.7</v>
+      </c>
+      <c r="C6">
+        <v>93.60000000000001</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>81.8</v>
+      </c>
+      <c r="F6">
+        <v>64</v>
+      </c>
+      <c r="G6">
+        <v>72.39999999999999</v>
+      </c>
+      <c r="H6">
+        <v>64.3</v>
+      </c>
+      <c r="I6">
+        <v>63.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7">
+        <v>92.7</v>
+      </c>
+      <c r="C7">
+        <v>98.2</v>
+      </c>
+      <c r="D7">
+        <v>99.5</v>
+      </c>
+      <c r="E7">
+        <v>99.7</v>
+      </c>
+      <c r="F7">
+        <v>95.3</v>
+      </c>
+      <c r="G7">
+        <v>57.99999999999999</v>
+      </c>
+      <c r="H7">
+        <v>56.00000000000001</v>
+      </c>
+      <c r="I7">
+        <v>59.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>98.3</v>
-      </c>
-      <c r="C6">
+      <c r="B8">
+        <v>98.5</v>
+      </c>
+      <c r="C8">
         <v>100</v>
       </c>
-      <c r="D6">
-        <v>100</v>
-      </c>
-      <c r="E6">
+      <c r="D8">
         <v>99.8</v>
       </c>
-      <c r="F6">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="G6">
-        <v>65.2</v>
-      </c>
-      <c r="H6">
-        <v>73.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="C7">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="D7">
-        <v>30.6</v>
-      </c>
-      <c r="E7">
-        <v>77.2</v>
-      </c>
-      <c r="F7">
-        <v>65</v>
-      </c>
-      <c r="G7">
-        <v>70.19999999999999</v>
-      </c>
-      <c r="H7">
-        <v>67.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8">
-        <v>89.8</v>
-      </c>
-      <c r="C8">
-        <v>98.8</v>
-      </c>
-      <c r="D8">
-        <v>99.2</v>
-      </c>
       <c r="E8">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="F8">
-        <v>94.89999999999999</v>
+        <v>92.60000000000001</v>
       </c>
       <c r="G8">
-        <v>62.5</v>
+        <v>65.5</v>
       </c>
       <c r="H8">
-        <v>64.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>57.09999999999999</v>
+      </c>
+      <c r="I8">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B9">
-        <v>98</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="C9">
-        <v>71.2</v>
+        <v>69.3</v>
       </c>
       <c r="D9">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="E9">
-        <v>15.9</v>
+        <v>14.7</v>
       </c>
       <c r="F9">
-        <v>12.6</v>
+        <v>11.5</v>
       </c>
       <c r="G9">
-        <v>33.6</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>32.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>30.4</v>
+      </c>
+      <c r="I9">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -2348,42 +2335,48 @@
         <v>0.1</v>
       </c>
       <c r="E10">
-        <v>10.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F10">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G10">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="H10">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="I10">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B11">
-        <v>33.5</v>
+        <v>31.2</v>
       </c>
       <c r="C11">
-        <v>30.8</v>
+        <v>34.1</v>
       </c>
       <c r="D11">
-        <v>7.000000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="E11">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="F11">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G11">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H11">
-        <v>0.3</v>
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2398,28 +2391,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2427,28 +2420,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>113.17</v>
+        <v>83.89</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>110.76</v>
+        <v>112.06</v>
       </c>
       <c r="G2">
-        <v>0.521</v>
+        <v>0.551</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2456,28 +2449,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>84.48999999999999</v>
+        <v>111.43</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>110.76</v>
+        <v>110.05</v>
       </c>
       <c r="G3">
-        <v>0.521</v>
+        <v>0.531</v>
       </c>
       <c r="H3">
         <v>3.6</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2485,28 +2478,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4">
-        <v>108.8</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>106.89</v>
+        <v>111.69</v>
       </c>
       <c r="G4">
-        <v>0.479</v>
+        <v>0.571</v>
       </c>
       <c r="H4">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2517,25 +2510,25 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5">
-        <v>119.81</v>
+        <v>119.4</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>106.89</v>
+        <v>106.88</v>
       </c>
       <c r="G5">
-        <v>0.479</v>
+        <v>0.49</v>
       </c>
       <c r="H5">
-        <v>0.9</v>
+        <v>-0.3</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2543,28 +2536,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D6">
-        <v>114.17</v>
+        <v>109.31</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6">
-        <v>109.59</v>
+        <v>107.54</v>
       </c>
       <c r="G6">
-        <v>0.542</v>
+        <v>0.49</v>
       </c>
       <c r="H6">
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2572,28 +2565,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D7">
-        <v>92.91</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>109.59</v>
+        <v>108.67</v>
       </c>
       <c r="G7">
-        <v>0.542</v>
+        <v>0.531</v>
       </c>
       <c r="H7">
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2601,28 +2594,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D8">
-        <v>102.1</v>
+        <v>129.22</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F8">
-        <v>108.84</v>
+        <v>104.96</v>
       </c>
       <c r="G8">
-        <v>0.5</v>
+        <v>0.469</v>
       </c>
       <c r="H8">
-        <v>-1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2630,28 +2623,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9">
-        <v>110.93</v>
+        <v>105.97</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9">
-        <v>108.84</v>
+        <v>102.91</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="H9">
-        <v>-1.6</v>
+        <v>-2</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2659,28 +2652,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D10">
-        <v>127.46</v>
+        <v>101.45</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10">
-        <v>105.8</v>
+        <v>106.4</v>
       </c>
       <c r="G10">
-        <v>0.458</v>
+        <v>0.49</v>
       </c>
       <c r="H10">
-        <v>-2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2691,25 +2684,25 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D11">
-        <v>109.93</v>
+        <v>105.04</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11">
-        <v>105.8</v>
+        <v>103.82</v>
       </c>
       <c r="G11">
-        <v>0.458</v>
+        <v>0.449</v>
       </c>
       <c r="H11">
-        <v>-2.4</v>
+        <v>-4</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2724,31 +2717,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2756,16 +2749,16 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D2">
-        <v>127.4566666666667</v>
+        <v>129.22</v>
       </c>
       <c r="E2">
-        <v>764.74</v>
+        <v>904.54</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -2774,10 +2767,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2785,28 +2778,28 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D3">
-        <v>119.81</v>
+        <v>119.4</v>
       </c>
       <c r="E3">
-        <v>718.86</v>
+        <v>835.8</v>
       </c>
       <c r="F3">
-        <v>96.8</v>
+        <v>99.5</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2814,28 +2807,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D4">
-        <v>113.1733333333333</v>
+        <v>111.4342857142857</v>
       </c>
       <c r="E4">
-        <v>679.04</v>
+        <v>780.04</v>
       </c>
       <c r="F4">
-        <v>86.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2843,115 +2836,115 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D5">
-        <v>114.1666666666667</v>
+        <v>114</v>
       </c>
       <c r="E5">
-        <v>685</v>
+        <v>798</v>
       </c>
       <c r="F5">
-        <v>78.2</v>
+        <v>90.60000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D6">
-        <v>109.9266666666667</v>
+        <v>109.3057142857143</v>
       </c>
       <c r="E6">
-        <v>659.5600000000001</v>
+        <v>765.1399999999999</v>
       </c>
       <c r="F6">
-        <v>73.5</v>
+        <v>67.5</v>
       </c>
       <c r="G6">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D7">
-        <v>110.93</v>
+        <v>105.9742857142857</v>
       </c>
       <c r="E7">
-        <v>665.5799999999999</v>
+        <v>741.8200000000001</v>
       </c>
       <c r="F7">
-        <v>69.09999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="G7">
         <v>0.1</v>
       </c>
       <c r="H7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D8">
-        <v>108.8</v>
+        <v>105.04</v>
       </c>
       <c r="E8">
-        <v>652.8000000000001</v>
+        <v>735.2800000000001</v>
       </c>
       <c r="F8">
-        <v>62.3</v>
+        <v>54.50000000000001</v>
       </c>
       <c r="G8">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2959,28 +2952,28 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C9">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="D9">
+        <v>101.4485714285714</v>
+      </c>
+      <c r="E9">
+        <v>710.14</v>
+      </c>
+      <c r="F9">
+        <v>29.8</v>
+      </c>
+      <c r="G9">
         <v>0.5</v>
       </c>
-      <c r="D9">
-        <v>102.1033333333333</v>
-      </c>
-      <c r="E9">
-        <v>612.62</v>
-      </c>
-      <c r="F9">
-        <v>32.4</v>
-      </c>
-      <c r="G9">
-        <v>0.1</v>
-      </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I9" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2988,28 +2981,28 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C10">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D10">
-        <v>92.90666666666668</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="E10">
-        <v>557.4400000000001</v>
+        <v>666.8200000000001</v>
       </c>
       <c r="F10">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="G10">
-        <v>24.8</v>
+        <v>7.7</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I10" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3017,28 +3010,28 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C11">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D11">
-        <v>84.48999999999999</v>
+        <v>83.89428571428572</v>
       </c>
       <c r="E11">
-        <v>506.9399999999999</v>
+        <v>587.26</v>
       </c>
       <c r="F11">
         <v>0.1</v>
       </c>
       <c r="G11">
-        <v>74.5</v>
+        <v>91.2</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I11" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -3053,19 +3046,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3079,13 +3072,13 @@
         <v>56</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3096,16 +3089,16 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3116,16 +3109,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3133,19 +3126,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D5">
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3153,19 +3146,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3173,10 +3166,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -3185,7 +3178,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3196,16 +3189,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3216,16 +3209,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3236,16 +3229,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3256,16 +3249,16 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3275,33 +3268,36 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>106</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -3323,11 +3319,14 @@
       <c r="G2">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -3349,11 +3348,14 @@
       <c r="G3">
         <v>11</v>
       </c>
-      <c r="H3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -3375,89 +3377,101 @@
       <c r="G4">
         <v>10</v>
       </c>
-      <c r="H4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4">
+        <v>8</v>
+      </c>
+      <c r="I4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
         <v>8</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
         <v>6</v>
       </c>
-      <c r="H5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B6">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>8</v>
+        <v>-6</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
-      <c r="H6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="D7">
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7">
         <v>2</v>
       </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>-6</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -3479,11 +3493,14 @@
       <c r="G8">
         <v>-4</v>
       </c>
-      <c r="H8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="H8">
+        <v>-5</v>
+      </c>
+      <c r="I8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -3505,11 +3522,14 @@
       <c r="G9">
         <v>-6</v>
       </c>
-      <c r="H9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="H9">
+        <v>-5</v>
+      </c>
+      <c r="I9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -3531,11 +3551,14 @@
       <c r="G10">
         <v>-10</v>
       </c>
-      <c r="H10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="H10">
+        <v>-8</v>
+      </c>
+      <c r="I10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>4</v>
       </c>
@@ -3557,8 +3580,11 @@
       <c r="G11">
         <v>-24</v>
       </c>
-      <c r="H11" t="s">
-        <v>96</v>
+      <c r="H11">
+        <v>-28</v>
+      </c>
+      <c r="I11" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Operators Football League 2026.xlsx
+++ b/data/leagues/Operators Football League 2026.xlsx
@@ -247,19 +247,19 @@
     <t>1-6</t>
   </si>
   <si>
-    <t>11.6-2.3-0.1</t>
-  </si>
-  <si>
-    <t>9.4-4.6-0.1</t>
+    <t>11.7-2.3-0.1</t>
+  </si>
+  <si>
+    <t>9.3-4.7-0.1</t>
   </si>
   <si>
     <t>8.6-5.3-0.1</t>
   </si>
   <si>
-    <t>7.8-6.1-0.1</t>
-  </si>
-  <si>
-    <t>6.7-7.3-0.1</t>
+    <t>7.9-6.0-0.1</t>
+  </si>
+  <si>
+    <t>6.6-7.4-0.1</t>
   </si>
   <si>
     <t>6.7-7.2-0.1</t>
@@ -268,13 +268,13 @@
     <t>6.6-7.3-0.1</t>
   </si>
   <si>
-    <t>6.0-8.0-0.1</t>
-  </si>
-  <si>
-    <t>4.0-9.9-0.1</t>
-  </si>
-  <si>
-    <t>2.3-11.7-0.1</t>
+    <t>6.0-7.9-0.1</t>
+  </si>
+  <si>
+    <t>4.1-9.9-0.1</t>
+  </si>
+  <si>
+    <t>2.2-11.7-0.1</t>
   </si>
   <si>
     <t>12-2</t>
@@ -286,10 +286,10 @@
     <t>8-6</t>
   </si>
   <si>
+    <t>6-8</t>
+  </si>
+  <si>
     <t>7-7</t>
-  </si>
-  <si>
-    <t>6-8</t>
   </si>
   <si>
     <t>4-10</t>
@@ -1678,19 +1678,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>90.3</v>
+        <v>91.5</v>
       </c>
       <c r="C2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="D2">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="E2">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1716,28 +1716,28 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>7.9</v>
+        <v>5.6</v>
       </c>
       <c r="C3">
-        <v>55.7</v>
+        <v>51.9</v>
       </c>
       <c r="D3">
-        <v>21.2</v>
+        <v>24.5</v>
       </c>
       <c r="E3">
-        <v>8.9</v>
+        <v>10.2</v>
       </c>
       <c r="F3">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="G3">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="H3">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1746,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.5</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1754,37 +1754,37 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>19.9</v>
+        <v>21.4</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>31.6</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>22.2</v>
       </c>
       <c r="F4">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="G4">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="H4">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="I4">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>96.5</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1792,37 +1792,37 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="C5">
-        <v>12.4</v>
+        <v>13.5</v>
       </c>
       <c r="D5">
-        <v>23.5</v>
+        <v>25.3</v>
       </c>
       <c r="E5">
-        <v>26.4</v>
+        <v>24.3</v>
       </c>
       <c r="F5">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="G5">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="I5">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J5">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>90.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1830,37 +1830,37 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D6">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="E6">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="F6">
-        <v>22.9</v>
+        <v>18.4</v>
       </c>
       <c r="G6">
-        <v>22.3</v>
+        <v>23.6</v>
       </c>
       <c r="H6">
-        <v>19</v>
+        <v>21.4</v>
       </c>
       <c r="I6">
         <v>11.4</v>
       </c>
       <c r="J6">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>0.2</v>
       </c>
       <c r="L6">
-        <v>67.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1871,34 +1871,34 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="D7">
-        <v>5.7</v>
+        <v>7.1</v>
       </c>
       <c r="E7">
-        <v>13.1</v>
+        <v>13.5</v>
       </c>
       <c r="F7">
-        <v>16.9</v>
+        <v>18.4</v>
       </c>
       <c r="G7">
-        <v>22.8</v>
+        <v>18.5</v>
       </c>
       <c r="H7">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="I7">
-        <v>16.5</v>
+        <v>19.3</v>
       </c>
       <c r="J7">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="K7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L7">
-        <v>59.8</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1906,37 +1906,37 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C8">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="D8">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="E8">
-        <v>10.1</v>
+        <v>10.8</v>
       </c>
       <c r="F8">
-        <v>17.8</v>
+        <v>18.2</v>
       </c>
       <c r="G8">
-        <v>18.9</v>
+        <v>21.3</v>
       </c>
       <c r="H8">
-        <v>22.7</v>
+        <v>21.3</v>
       </c>
       <c r="I8">
         <v>18</v>
       </c>
       <c r="J8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K8">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L8">
-        <v>54.5</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1947,34 +1947,34 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D9">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="E9">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="F9">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="G9">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="H9">
         <v>24.5</v>
       </c>
       <c r="I9">
-        <v>35.6</v>
+        <v>34.6</v>
       </c>
       <c r="J9">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K9">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="L9">
-        <v>29.8</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1991,28 +1991,28 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F10">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="G10">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="H10">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="I10">
-        <v>14.3</v>
+        <v>13.1</v>
       </c>
       <c r="J10">
-        <v>71.8</v>
+        <v>72.2</v>
       </c>
       <c r="K10">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="L10">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2035,22 +2035,22 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J11">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="K11">
-        <v>91.2</v>
+        <v>92.5</v>
       </c>
       <c r="L11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2094,10 +2094,10 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -2106,7 +2106,7 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G2">
         <v>100</v>
@@ -2123,25 +2123,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="D3">
-        <v>88.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="E3">
-        <v>83.89999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="F3">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="G3">
-        <v>96.39999999999999</v>
+        <v>96</v>
       </c>
       <c r="H3">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="I3">
         <v>99.09999999999999</v>
@@ -2152,28 +2152,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>79.3</v>
+        <v>81.10000000000001</v>
       </c>
       <c r="C4">
-        <v>35.6</v>
+        <v>37</v>
       </c>
       <c r="D4">
-        <v>93.30000000000001</v>
+        <v>95</v>
       </c>
       <c r="E4">
-        <v>94.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F4">
-        <v>88.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="G4">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H4">
-        <v>95.8</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="I4">
-        <v>96.59999999999999</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2184,25 +2184,25 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>36.2</v>
+        <v>36.9</v>
       </c>
       <c r="D5">
-        <v>40.5</v>
+        <v>37.3</v>
       </c>
       <c r="E5">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="F5">
-        <v>47.5</v>
+        <v>46.9</v>
       </c>
       <c r="G5">
-        <v>81.39999999999999</v>
+        <v>80.60000000000001</v>
       </c>
       <c r="H5">
-        <v>91.8</v>
+        <v>92.60000000000001</v>
       </c>
       <c r="I5">
-        <v>90.90000000000001</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2210,28 +2210,28 @@
         <v>2</v>
       </c>
       <c r="B6">
-        <v>99.7</v>
+        <v>99.3</v>
       </c>
       <c r="C6">
-        <v>93.60000000000001</v>
+        <v>93.89999999999999</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>32.2</v>
       </c>
       <c r="E6">
-        <v>81.8</v>
+        <v>79.3</v>
       </c>
       <c r="F6">
-        <v>64</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="G6">
         <v>72.39999999999999</v>
       </c>
       <c r="H6">
-        <v>64.3</v>
+        <v>66.7</v>
       </c>
       <c r="I6">
-        <v>63.3</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2239,28 +2239,28 @@
         <v>0</v>
       </c>
       <c r="B7">
-        <v>92.7</v>
+        <v>92.5</v>
       </c>
       <c r="C7">
-        <v>98.2</v>
+        <v>97.39999999999999</v>
       </c>
       <c r="D7">
-        <v>99.5</v>
+        <v>99.3</v>
       </c>
       <c r="E7">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>95.3</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="G7">
-        <v>57.99999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="H7">
         <v>56.00000000000001</v>
       </c>
       <c r="I7">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2268,28 +2268,28 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>98.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="C8">
         <v>100</v>
       </c>
       <c r="D8">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E8">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
       <c r="F8">
-        <v>92.60000000000001</v>
+        <v>91</v>
       </c>
       <c r="G8">
-        <v>65.5</v>
+        <v>65.10000000000001</v>
       </c>
       <c r="H8">
-        <v>57.09999999999999</v>
+        <v>54.50000000000001</v>
       </c>
       <c r="I8">
-        <v>56.8</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2297,28 +2297,28 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>98.40000000000001</v>
+        <v>97.89999999999999</v>
       </c>
       <c r="C9">
-        <v>69.3</v>
+        <v>69.89999999999999</v>
       </c>
       <c r="D9">
-        <v>42.4</v>
+        <v>40.40000000000001</v>
       </c>
       <c r="E9">
-        <v>14.7</v>
+        <v>16.1</v>
       </c>
       <c r="F9">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="G9">
-        <v>34</v>
+        <v>31.6</v>
       </c>
       <c r="H9">
-        <v>30.4</v>
+        <v>32.6</v>
       </c>
       <c r="I9">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2332,22 +2332,22 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="F10">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G10">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H10">
-        <v>5.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="I10">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2355,22 +2355,22 @@
         <v>4</v>
       </c>
       <c r="B11">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="C11">
-        <v>34.1</v>
+        <v>32.5</v>
       </c>
       <c r="D11">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
       <c r="E11">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="F11">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G11">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -2790,7 +2790,7 @@
         <v>835.8</v>
       </c>
       <c r="F3">
-        <v>99.5</v>
+        <v>98.5</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2819,7 +2819,7 @@
         <v>780.04</v>
       </c>
       <c r="F4">
-        <v>96.5</v>
+        <v>96.8</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>798</v>
       </c>
       <c r="F5">
-        <v>90.60000000000001</v>
+        <v>92.10000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2877,7 +2877,7 @@
         <v>765.1399999999999</v>
       </c>
       <c r="F6">
-        <v>67.5</v>
+        <v>63</v>
       </c>
       <c r="G6">
         <v>0.2</v>
@@ -2906,16 +2906,16 @@
         <v>741.8200000000001</v>
       </c>
       <c r="F7">
-        <v>59.8</v>
+        <v>59.4</v>
       </c>
       <c r="G7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H7" t="s">
         <v>79</v>
       </c>
       <c r="I7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2935,16 +2935,16 @@
         <v>735.2800000000001</v>
       </c>
       <c r="F8">
-        <v>54.50000000000001</v>
+        <v>55.90000000000001</v>
       </c>
       <c r="G8">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H8" t="s">
         <v>80</v>
       </c>
       <c r="I8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2964,16 +2964,16 @@
         <v>710.14</v>
       </c>
       <c r="F9">
-        <v>29.8</v>
+        <v>31.5</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H9" t="s">
         <v>81</v>
       </c>
       <c r="I9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2993,10 +2993,10 @@
         <v>666.8200000000001</v>
       </c>
       <c r="F10">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="G10">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="s">
         <v>82</v>
@@ -3022,10 +3022,10 @@
         <v>587.26</v>
       </c>
       <c r="F11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>91.2</v>
+        <v>92.5</v>
       </c>
       <c r="H11" t="s">
         <v>83</v>
@@ -3186,19 +3186,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>-5</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3206,19 +3206,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9">
         <v>-5</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3473,60 +3473,60 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
         <v>-2</v>
       </c>
-      <c r="C8">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>-2</v>
+      </c>
+      <c r="F8">
         <v>-4</v>
       </c>
-      <c r="D8">
-        <v>-5</v>
-      </c>
-      <c r="E8">
-        <v>-4</v>
-      </c>
-      <c r="F8">
-        <v>-7</v>
-      </c>
       <c r="G8">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="H8">
         <v>-5</v>
       </c>
       <c r="I8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="C9">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="E9">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="F9">
+        <v>-7</v>
+      </c>
+      <c r="G9">
         <v>-4</v>
-      </c>
-      <c r="G9">
-        <v>-6</v>
       </c>
       <c r="H9">
         <v>-5</v>
       </c>
       <c r="I9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:9">
